--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379819</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,879 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126585102</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80119</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>723312</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7215920</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126585094</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80083</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>723310</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7215915</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126585285</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>723281</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7216191</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126585491</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723276</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7216268</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126585362</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723309</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7216242</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126585576</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>723253</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7216261</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126585609</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97239</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>723248</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7216291</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126585723</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105381</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>723251</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7216315</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126585671</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105381</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Snottermyran, Snottermyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>723241</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7216303</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126585576</v>
+        <v>126585609</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>97239</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723253</v>
+        <v>723248</v>
       </c>
       <c r="R8" t="n">
-        <v>7216261</v>
+        <v>7216291</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,32 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126585609</v>
+        <v>126585576</v>
       </c>
       <c r="B9" t="n">
-        <v>97239</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723248</v>
+        <v>723253</v>
       </c>
       <c r="R9" t="n">
-        <v>7216291</v>
+        <v>7216261</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126585102</v>
       </c>
       <c r="B3" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126585285</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126585094</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126585491</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126585362</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,32 +1266,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126585609</v>
+        <v>126585576</v>
       </c>
       <c r="B8" t="n">
-        <v>97239</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723248</v>
+        <v>723253</v>
       </c>
       <c r="R8" t="n">
-        <v>7216291</v>
+        <v>7216261</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1363,32 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126585576</v>
+        <v>126585609</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>97314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723253</v>
+        <v>723248</v>
       </c>
       <c r="R9" t="n">
-        <v>7216261</v>
+        <v>7216291</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>126585723</v>
       </c>
       <c r="B10" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126585671</v>
       </c>
       <c r="B11" t="n">
-        <v>105381</v>
+        <v>105456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,53 +1654,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020059</v>
+        <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>91677</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723530</v>
+        <v>723592</v>
       </c>
       <c r="R12" t="n">
-        <v>7216208</v>
+        <v>7216220</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1733,11 +1725,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1764,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020023</v>
+        <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>91603</v>
+        <v>92802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723592</v>
+        <v>723341</v>
       </c>
       <c r="R13" t="n">
-        <v>7216220</v>
+        <v>7215856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020068</v>
+        <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>92727</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1872,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723341</v>
+        <v>723589</v>
       </c>
       <c r="R14" t="n">
-        <v>7215856</v>
+        <v>7216289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020095</v>
+        <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,34 +1956,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723589</v>
+        <v>723530</v>
       </c>
       <c r="R15" t="n">
-        <v>7216289</v>
+        <v>7216208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,6 +2024,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020018</v>
+        <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723548</v>
+        <v>723233</v>
       </c>
       <c r="R16" t="n">
-        <v>7215979</v>
+        <v>7216428</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>127020018</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723548</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7215979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
         <v>127020098</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>78769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2448,10 +2443,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020062</v>
+        <v>127020083</v>
       </c>
       <c r="B20" t="n">
-        <v>92539</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2459,21 +2454,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2483,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723192</v>
+        <v>723241</v>
       </c>
       <c r="R20" t="n">
-        <v>7216368</v>
+        <v>7216310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2519,6 +2514,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2545,32 +2545,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020079</v>
+        <v>127020062</v>
       </c>
       <c r="B21" t="n">
-        <v>78738</v>
+        <v>92613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723330</v>
+        <v>723192</v>
       </c>
       <c r="R21" t="n">
-        <v>7216112</v>
+        <v>7216368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,7 +2645,7 @@
         <v>127020093</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020033</v>
+        <v>127020016</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,42 +2750,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723480</v>
+        <v>723237</v>
       </c>
       <c r="R23" t="n">
-        <v>7215979</v>
+        <v>7216401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,11 +2810,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2852,7 +2839,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2946,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020067</v>
+        <v>127020033</v>
       </c>
       <c r="B25" t="n">
-        <v>92727</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,34 +2944,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723414</v>
+        <v>723480</v>
       </c>
       <c r="R25" t="n">
-        <v>7216002</v>
+        <v>7215979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3017,6 +3012,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>92802</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R26" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,34 +3151,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R27" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,13 +3225,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>78770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,46 +3265,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R28" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,17 +3327,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3352,45 +3352,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020080</v>
+        <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>78738</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723686</v>
+        <v>723659</v>
       </c>
       <c r="R29" t="n">
-        <v>7216284</v>
+        <v>7216289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,6 +3431,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3449,53 +3462,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020049</v>
+        <v>127020081</v>
       </c>
       <c r="B30" t="n">
-        <v>56849</v>
+        <v>78769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723659</v>
+        <v>723396</v>
       </c>
       <c r="R30" t="n">
-        <v>7216289</v>
+        <v>7215995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3528,11 +3533,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3559,32 +3559,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020057</v>
+        <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>98382</v>
+        <v>78769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723541</v>
+        <v>723686</v>
       </c>
       <c r="R31" t="n">
-        <v>7216191</v>
+        <v>7216284</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3659,7 +3659,7 @@
         <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3753,32 +3753,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020081</v>
+        <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>78738</v>
+        <v>98457</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723396</v>
+        <v>723541</v>
       </c>
       <c r="R33" t="n">
-        <v>7215995</v>
+        <v>7216191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92539</v>
+        <v>92613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020026</v>
+        <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,16 +3958,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723085</v>
+        <v>723333</v>
       </c>
       <c r="R35" t="n">
-        <v>7216102</v>
+        <v>7216135</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,7 +4057,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020032</v>
+        <v>127020026</v>
       </c>
       <c r="B36" t="n">
         <v>57657</v>
@@ -4090,7 +4090,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4100,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723539</v>
+        <v>723085</v>
       </c>
       <c r="R36" t="n">
-        <v>7215974</v>
+        <v>7216102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B37" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,16 +4178,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4200,7 +4200,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R37" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,7 +4280,7 @@
         <v>127020017</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,42 +4580,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4648,11 +4640,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,10 +4666,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020096</v>
+        <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,34 +4677,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723595</v>
+        <v>723592</v>
       </c>
       <c r="R42" t="n">
-        <v>7216276</v>
+        <v>7216060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4750,6 +4745,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4779,7 +4779,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020112</v>
+        <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723697</v>
+        <v>723538</v>
       </c>
       <c r="R45" t="n">
-        <v>7216227</v>
+        <v>7216303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020111</v>
+        <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723538</v>
+        <v>723697</v>
       </c>
       <c r="R46" t="n">
-        <v>7216303</v>
+        <v>7216227</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,7 +5180,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>78739</v>
+        <v>57817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,34 +5505,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R50" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,13 +5575,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5595,7 +5607,7 @@
         <v>127020082</v>
       </c>
       <c r="B51" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5689,10 +5701,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020053</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>78770</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,42 +5712,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723526</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7216153</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5770,17 +5774,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lock</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020097</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>91580</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723576</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7216143</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5899,7 +5899,7 @@
         <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>127020110</v>
       </c>
       <c r="B55" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6190,7 +6190,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020035</v>
+        <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,42 +6296,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723333</v>
+        <v>723509</v>
       </c>
       <c r="R58" t="n">
-        <v>7215846</v>
+        <v>7216058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,17 +6350,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6395,10 +6382,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020094</v>
+        <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,34 +6393,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723509</v>
+        <v>723333</v>
       </c>
       <c r="R59" t="n">
-        <v>7216058</v>
+        <v>7215846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6460,12 +6455,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6492,32 +6492,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B60" t="n">
-        <v>57761</v>
+        <v>78770</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R60" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,6 +6571,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6699,32 +6700,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B62" t="n">
-        <v>78739</v>
+        <v>57761</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6734,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R62" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6778,7 +6779,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6797,45 +6797,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>98361</v>
+        <v>57817</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R63" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6872,7 +6880,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6902,7 +6910,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90283</v>
+        <v>90354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6996,53 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>57817</v>
+        <v>98436</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723260</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7216304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7109,7 +7109,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126585102</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126585285</v>
+        <v>126585094</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723281</v>
+        <v>723310</v>
       </c>
       <c r="R4" t="n">
-        <v>7216191</v>
+        <v>7215915</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126585094</v>
+        <v>126585285</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723310</v>
+        <v>723281</v>
       </c>
       <c r="R5" t="n">
-        <v>7215915</v>
+        <v>7216191</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126585491</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126585362</v>
       </c>
       <c r="B7" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126585576</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>126585609</v>
       </c>
       <c r="B9" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>126585723</v>
       </c>
       <c r="B10" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126585671</v>
       </c>
       <c r="B11" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B12" t="n">
-        <v>91677</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R12" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020068</v>
+        <v>127020023</v>
       </c>
       <c r="B13" t="n">
-        <v>92802</v>
+        <v>91683</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723341</v>
+        <v>723592</v>
       </c>
       <c r="R13" t="n">
-        <v>7215856</v>
+        <v>7216220</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020095</v>
+        <v>127020068</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>92808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723589</v>
+        <v>723341</v>
       </c>
       <c r="R14" t="n">
-        <v>7216289</v>
+        <v>7215856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
         <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,10 +2152,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020018</v>
+        <v>127020098</v>
       </c>
       <c r="B17" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2163,21 +2163,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723548</v>
+        <v>723581</v>
       </c>
       <c r="R17" t="n">
-        <v>7215979</v>
+        <v>7216130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020098</v>
+        <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723581</v>
+        <v>723548</v>
       </c>
       <c r="R18" t="n">
-        <v>7216130</v>
+        <v>7215979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>92619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723192</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216368</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,32 +2443,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R20" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,11 +2514,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2545,10 +2540,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020062</v>
+        <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>92613</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2556,21 +2551,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723192</v>
+        <v>723241</v>
       </c>
       <c r="R21" t="n">
-        <v>7216368</v>
+        <v>7216310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020093</v>
+        <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,34 +2653,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723104</v>
+        <v>723480</v>
       </c>
       <c r="R22" t="n">
-        <v>7215946</v>
+        <v>7215979</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2739,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020016</v>
+        <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2774,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723237</v>
+        <v>723104</v>
       </c>
       <c r="R23" t="n">
-        <v>7216401</v>
+        <v>7215946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020016</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723237</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7216401</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020033</v>
+        <v>127020101</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,42 +2957,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723480</v>
+        <v>723341</v>
       </c>
       <c r="R25" t="n">
-        <v>7215979</v>
+        <v>7215856</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,11 +3017,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3046,7 +3046,7 @@
         <v>127020067</v>
       </c>
       <c r="B26" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,53 +3352,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020049</v>
+        <v>127020080</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723659</v>
+        <v>723686</v>
       </c>
       <c r="R29" t="n">
-        <v>7216289</v>
+        <v>7216284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,11 +3423,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3465,7 +3452,7 @@
         <v>127020081</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020080</v>
+        <v>127020117</v>
       </c>
       <c r="B31" t="n">
-        <v>78769</v>
+        <v>78420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3570,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3594,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723686</v>
+        <v>723317</v>
       </c>
       <c r="R31" t="n">
-        <v>7216284</v>
+        <v>7216136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,45 +3643,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020117</v>
+        <v>127020049</v>
       </c>
       <c r="B32" t="n">
-        <v>78417</v>
+        <v>56849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723317</v>
+        <v>723659</v>
       </c>
       <c r="R32" t="n">
-        <v>7216136</v>
+        <v>7216289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,6 +3722,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3756,7 +3756,7 @@
         <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92613</v>
+        <v>92619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020060</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723333</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7216135</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020026</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4100,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723085</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7216102</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4167,7 +4154,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020032</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
         <v>57657</v>
@@ -4200,7 +4187,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4210,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723539</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7215974</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020017</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>79629</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4288,34 +4275,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723183</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216366</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4343,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4377,7 +4377,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,45 +4776,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R43" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,6 +4855,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4873,53 +4886,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B44" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R44" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4952,11 +4957,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4986,7 +4986,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020053</v>
+        <v>127020082</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>78772</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,42 +5505,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723526</v>
+        <v>723348</v>
       </c>
       <c r="R50" t="n">
-        <v>7216153</v>
+        <v>7215836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5615,21 +5602,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R51" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5683,6 +5670,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B52" t="n">
-        <v>78770</v>
+        <v>57817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,34 +5700,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R52" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,13 +5770,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020073</v>
       </c>
       <c r="B53" t="n">
-        <v>91580</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723348</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7215836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5878,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5896,32 +5897,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>82852</v>
+        <v>91586</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5932,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5994,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B55" t="n">
-        <v>92609</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R55" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,10 +6091,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>82855</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6101,21 +6102,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6187,32 +6188,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>127020110</v>
       </c>
       <c r="B57" t="n">
-        <v>78770</v>
+        <v>92615</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6222,10 +6223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723323</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216249</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6266,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>127020069</v>
       </c>
       <c r="B60" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6797,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B63" t="n">
-        <v>57817</v>
+        <v>90360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,42 +6808,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R63" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6876,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6907,32 +6894,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020020</v>
+        <v>127020084</v>
       </c>
       <c r="B64" t="n">
-        <v>90354</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6942,10 +6929,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723341</v>
+        <v>723260</v>
       </c>
       <c r="R64" t="n">
-        <v>7216126</v>
+        <v>7216304</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6978,6 +6965,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7004,45 +6996,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>98436</v>
+        <v>57817</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R65" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7109,7 +7109,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -878,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126585094</v>
+        <v>126585285</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723310</v>
+        <v>723281</v>
       </c>
       <c r="R4" t="n">
-        <v>7215915</v>
+        <v>7216191</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,32 +975,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126585285</v>
+        <v>126585094</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723281</v>
+        <v>723310</v>
       </c>
       <c r="R5" t="n">
-        <v>7216191</v>
+        <v>7215915</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126585609</v>
+        <v>126585723</v>
       </c>
       <c r="B9" t="n">
-        <v>97320</v>
+        <v>105462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723248</v>
+        <v>723251</v>
       </c>
       <c r="R9" t="n">
-        <v>7216291</v>
+        <v>7216315</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126585723</v>
+        <v>126585609</v>
       </c>
       <c r="B10" t="n">
-        <v>105462</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723251</v>
+        <v>723248</v>
       </c>
       <c r="R10" t="n">
-        <v>7216315</v>
+        <v>7216291</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020095</v>
+        <v>127020068</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723589</v>
+        <v>723341</v>
       </c>
       <c r="R12" t="n">
-        <v>7216289</v>
+        <v>7215856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,32 +1751,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B13" t="n">
-        <v>91683</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R13" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020068</v>
+        <v>127020059</v>
       </c>
       <c r="B14" t="n">
-        <v>92808</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,34 +1859,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723341</v>
+        <v>723530</v>
       </c>
       <c r="R14" t="n">
-        <v>7215856</v>
+        <v>7216208</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1919,6 +1927,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1945,53 +1958,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020059</v>
+        <v>127020023</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>91683</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723530</v>
+        <v>723592</v>
       </c>
       <c r="R15" t="n">
-        <v>7216208</v>
+        <v>7216220</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2024,11 +2029,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,10 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020062</v>
+        <v>127020083</v>
       </c>
       <c r="B19" t="n">
-        <v>92619</v>
+        <v>98442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723192</v>
+        <v>723241</v>
       </c>
       <c r="R19" t="n">
-        <v>7216368</v>
+        <v>7216310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,6 +2417,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,10 +2545,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>92619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2551,21 +2556,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2611,11 +2616,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2752,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020093</v>
+        <v>127020016</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723104</v>
+        <v>723237</v>
       </c>
       <c r="R23" t="n">
-        <v>7215946</v>
+        <v>7216401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B24" t="n">
-        <v>79632</v>
+        <v>92808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R24" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020067</v>
+        <v>127020093</v>
       </c>
       <c r="B26" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723414</v>
+        <v>723104</v>
       </c>
       <c r="R26" t="n">
-        <v>7216002</v>
+        <v>7215946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,45 +3352,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020080</v>
+        <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723686</v>
+        <v>723659</v>
       </c>
       <c r="R29" t="n">
-        <v>7216284</v>
+        <v>7216289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,6 +3431,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3546,10 +3559,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020117</v>
+        <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3570,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723317</v>
+        <v>723686</v>
       </c>
       <c r="R31" t="n">
-        <v>7216136</v>
+        <v>7216284</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,53 +3656,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020049</v>
+        <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>78420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723659</v>
+        <v>723317</v>
       </c>
       <c r="R32" t="n">
-        <v>7216289</v>
+        <v>7216136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3722,11 +3727,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4044,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020026</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723085</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7216102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,7 +4154,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020032</v>
       </c>
       <c r="B37" t="n">
         <v>57657</v>
@@ -4187,7 +4187,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723539</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7215974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,53 +4776,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R43" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,11 +4847,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,45 +4873,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R44" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4957,6 +4952,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020027</v>
       </c>
       <c r="B47" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,34 +5188,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723273</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5256,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,42 +5298,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5353,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5591,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B51" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,34 +5602,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R51" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5664,13 +5672,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5701,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020053</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,42 +5712,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723526</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7216153</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5770,17 +5774,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lock</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020073</v>
+        <v>127020105</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>82855</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723348</v>
+        <v>723580</v>
       </c>
       <c r="R53" t="n">
-        <v>7215836</v>
+        <v>7216146</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,7 +5878,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5897,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>91586</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5932,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5994,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020097</v>
+        <v>127020110</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723576</v>
+        <v>723323</v>
       </c>
       <c r="R55" t="n">
-        <v>7216143</v>
+        <v>7216249</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6091,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B56" t="n">
-        <v>82855</v>
+        <v>91586</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6126,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R56" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,32 +6187,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020110</v>
+        <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>92615</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6223,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723323</v>
+        <v>723348</v>
       </c>
       <c r="R57" t="n">
-        <v>7216249</v>
+        <v>7215836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B60" t="n">
-        <v>78773</v>
+        <v>57761</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R60" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,7 +6571,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6590,10 +6589,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020058</v>
+        <v>127020069</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6601,42 +6600,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723561</v>
+        <v>723237</v>
       </c>
       <c r="R61" t="n">
-        <v>7216205</v>
+        <v>7216401</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6671,17 +6662,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6700,27 +6687,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020076</v>
+        <v>127020058</v>
       </c>
       <c r="B62" t="n">
-        <v>57761</v>
+        <v>57654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6729,16 +6716,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723707</v>
+        <v>723561</v>
       </c>
       <c r="R62" t="n">
-        <v>7216227</v>
+        <v>7216205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6894,45 +6894,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R64" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6969,7 +6977,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6996,53 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723260</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7216304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7106,10 +7106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127020099</v>
+        <v>127020030</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7117,34 +7117,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723570</v>
+        <v>723726</v>
       </c>
       <c r="R66" t="n">
-        <v>7216008</v>
+        <v>7216246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7177,6 +7189,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7203,10 +7220,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127020030</v>
+        <v>127020099</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7214,46 +7231,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723726</v>
+        <v>723570</v>
       </c>
       <c r="R67" t="n">
-        <v>7216246</v>
+        <v>7216008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7286,11 +7291,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020033</v>
+        <v>127020016</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,42 +2653,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723480</v>
+        <v>723237</v>
       </c>
       <c r="R22" t="n">
-        <v>7215979</v>
+        <v>7216401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,11 +2713,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2752,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>92808</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,21 +2750,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R23" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020067</v>
+        <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723414</v>
+        <v>723341</v>
       </c>
       <c r="R24" t="n">
-        <v>7216002</v>
+        <v>7215856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,7 +2933,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020101</v>
+        <v>127020093</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -2981,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723341</v>
+        <v>723104</v>
       </c>
       <c r="R25" t="n">
-        <v>7215856</v>
+        <v>7215946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3043,10 +3030,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020093</v>
+        <v>127020033</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,34 +3041,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723104</v>
+        <v>723480</v>
       </c>
       <c r="R26" t="n">
-        <v>7215946</v>
+        <v>7215979</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,6 +3109,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>91325</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,42 +5188,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R47" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5256,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020024</v>
+        <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>91325</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,34 +5285,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723587</v>
+        <v>723273</v>
       </c>
       <c r="R48" t="n">
-        <v>7216223</v>
+        <v>7216111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5353,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>82855</v>
+        <v>91586</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,10 +5896,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5907,21 +5907,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B55" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R55" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020107</v>
+        <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>91586</v>
+        <v>92615</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723230</v>
+        <v>723323</v>
       </c>
       <c r="R56" t="n">
-        <v>7216412</v>
+        <v>7216249</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6492,27 +6492,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020076</v>
+        <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57761</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6521,16 +6521,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723707</v>
+        <v>723561</v>
       </c>
       <c r="R60" t="n">
-        <v>7216227</v>
+        <v>7216205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6563,6 +6571,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6589,32 +6602,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>57761</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6624,10 +6637,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R61" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6668,7 +6681,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6687,10 +6699,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020058</v>
+        <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6698,42 +6710,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723561</v>
+        <v>723237</v>
       </c>
       <c r="R62" t="n">
-        <v>7216205</v>
+        <v>7216401</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6768,17 +6772,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020068</v>
+        <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>92808</v>
+        <v>91684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723341</v>
+        <v>723592</v>
       </c>
       <c r="R12" t="n">
-        <v>7215856</v>
+        <v>7216220</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020095</v>
+        <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723589</v>
+        <v>723341</v>
       </c>
       <c r="R13" t="n">
-        <v>7216289</v>
+        <v>7215856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1958,32 +1958,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B15" t="n">
-        <v>91683</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R15" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020109</v>
+        <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723233</v>
+        <v>723581</v>
       </c>
       <c r="R16" t="n">
-        <v>7216428</v>
+        <v>7216130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R17" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>98442</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,21 +2357,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R19" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,10 +2540,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020062</v>
+        <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>92619</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2556,21 +2551,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723192</v>
+        <v>723241</v>
       </c>
       <c r="R21" t="n">
-        <v>7216368</v>
+        <v>7216310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R22" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020067</v>
+        <v>127020101</v>
       </c>
       <c r="B23" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723414</v>
+        <v>723341</v>
       </c>
       <c r="R23" t="n">
-        <v>7216002</v>
+        <v>7215856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020033</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,34 +2847,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723480</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7215979</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2907,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020033</v>
+        <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3041,42 +3054,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723480</v>
+        <v>723237</v>
       </c>
       <c r="R26" t="n">
-        <v>7215979</v>
+        <v>7216401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,11 +3114,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,10 +3352,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020049</v>
+        <v>127020057</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>98464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3363,42 +3363,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723659</v>
+        <v>723541</v>
       </c>
       <c r="R29" t="n">
-        <v>7216289</v>
+        <v>7216191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,11 +3423,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,10 +3740,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020057</v>
+        <v>127020049</v>
       </c>
       <c r="B33" t="n">
-        <v>98463</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3764,34 +3751,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723541</v>
+        <v>723659</v>
       </c>
       <c r="R33" t="n">
-        <v>7216191</v>
+        <v>7216289</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,6 +3819,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92619</v>
+        <v>92620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020026</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723085</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7216102</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,7 +4154,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020032</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
         <v>57657</v>
@@ -4187,7 +4187,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723539</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7215974</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R40" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R41" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020056</v>
       </c>
       <c r="B47" t="n">
-        <v>91325</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,34 +5188,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723286</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216268</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5256,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,42 +5298,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5353,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020056</v>
+        <v>127020027</v>
       </c>
       <c r="B49" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723286</v>
+        <v>723273</v>
       </c>
       <c r="R49" t="n">
-        <v>7216268</v>
+        <v>7216111</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B50" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,21 +5505,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R50" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,6 +5573,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5591,10 +5592,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020053</v>
+        <v>127020082</v>
       </c>
       <c r="B51" t="n">
-        <v>57817</v>
+        <v>78772</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,42 +5603,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723526</v>
+        <v>723348</v>
       </c>
       <c r="R51" t="n">
-        <v>7216153</v>
+        <v>7215836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5670,11 +5663,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5701,10 +5689,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,34 +5700,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R52" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,13 +5770,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020073</v>
       </c>
       <c r="B53" t="n">
-        <v>91586</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723348</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7215836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5878,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5896,32 +5897,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>82855</v>
+        <v>91587</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5932,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,10 +5994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6004,21 +6005,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6091,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6187,32 +6188,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>127020110</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6222,10 +6223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723323</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216249</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6266,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6492,27 +6492,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020058</v>
+        <v>127020076</v>
       </c>
       <c r="B60" t="n">
-        <v>57654</v>
+        <v>57761</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6521,24 +6521,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723561</v>
+        <v>723707</v>
       </c>
       <c r="R60" t="n">
-        <v>7216205</v>
+        <v>7216227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,11 +6563,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6602,32 +6589,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B61" t="n">
-        <v>57761</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6637,10 +6624,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R61" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,6 +6668,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6699,10 +6687,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020069</v>
+        <v>127020058</v>
       </c>
       <c r="B62" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6710,34 +6698,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723237</v>
+        <v>723561</v>
       </c>
       <c r="R62" t="n">
-        <v>7216401</v>
+        <v>7216205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6772,13 +6768,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6797,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020020</v>
+        <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>90360</v>
+        <v>57817</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,34 +6808,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723341</v>
+        <v>723650</v>
       </c>
       <c r="R63" t="n">
-        <v>7216126</v>
+        <v>7216234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6876,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>57817</v>
+        <v>90361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6905,42 +6918,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R64" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,11 +6978,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7007,7 +7007,7 @@
         <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020057</v>
+        <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>98464</v>
+        <v>56849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3363,34 +3363,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723541</v>
+        <v>723659</v>
       </c>
       <c r="R29" t="n">
-        <v>7216191</v>
+        <v>7216289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,6 +3431,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3449,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020081</v>
+        <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>98464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3484,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723396</v>
+        <v>723541</v>
       </c>
       <c r="R30" t="n">
-        <v>7215995</v>
+        <v>7216191</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,7 +3559,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020080</v>
+        <v>127020081</v>
       </c>
       <c r="B31" t="n">
         <v>78772</v>
@@ -3581,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723686</v>
+        <v>723396</v>
       </c>
       <c r="R31" t="n">
-        <v>7216284</v>
+        <v>7215995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,10 +3656,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020117</v>
+        <v>127020080</v>
       </c>
       <c r="B32" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3654,21 +3667,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3678,10 +3691,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723317</v>
+        <v>723686</v>
       </c>
       <c r="R32" t="n">
-        <v>7216136</v>
+        <v>7216284</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3740,53 +3753,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020049</v>
+        <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>78420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723659</v>
+        <v>723317</v>
       </c>
       <c r="R33" t="n">
-        <v>7216289</v>
+        <v>7216136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,11 +3824,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723333</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7216135</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,42 +4068,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723183</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7216366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,11 +4128,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>127020031</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,34 +4483,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723592</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7216060</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4543,6 +4551,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4569,10 +4582,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,21 +4593,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4617,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4666,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020031</v>
+        <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,42 +4690,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723592</v>
+        <v>723486</v>
       </c>
       <c r="R42" t="n">
-        <v>7216060</v>
+        <v>7215989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4745,11 +4750,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020073</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>91587</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723348</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7215836</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,7 +5878,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5897,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>91587</v>
+        <v>82855</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5932,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5994,10 +5993,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020097</v>
       </c>
       <c r="B55" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6005,21 +6004,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723576</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6091,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6126,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723323</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7216249</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,32 +6187,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020110</v>
+        <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6223,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723323</v>
+        <v>723348</v>
       </c>
       <c r="R57" t="n">
-        <v>7216249</v>
+        <v>7215836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127020030</v>
+        <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7117,46 +7117,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723726</v>
+        <v>723570</v>
       </c>
       <c r="R66" t="n">
-        <v>7216246</v>
+        <v>7216008</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7189,11 +7177,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7220,10 +7203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127020099</v>
+        <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7231,34 +7214,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723570</v>
+        <v>723726</v>
       </c>
       <c r="R67" t="n">
-        <v>7216008</v>
+        <v>7216246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,6 +7286,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020059</v>
+        <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,42 +1859,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723530</v>
+        <v>723589</v>
       </c>
       <c r="R14" t="n">
-        <v>7216208</v>
+        <v>7216289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1927,11 +1919,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1958,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020095</v>
+        <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,34 +1956,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723589</v>
+        <v>723530</v>
       </c>
       <c r="R15" t="n">
-        <v>7216289</v>
+        <v>7216208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,6 +2024,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R16" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>127020098</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723581</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7216130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>78772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,32 +2443,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R20" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,6 +2514,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2540,10 +2545,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2551,21 +2556,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2611,11 +2616,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020067</v>
+        <v>127020093</v>
       </c>
       <c r="B22" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723414</v>
+        <v>723104</v>
       </c>
       <c r="R22" t="n">
-        <v>7216002</v>
+        <v>7215946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020101</v>
+        <v>127020067</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723341</v>
+        <v>723414</v>
       </c>
       <c r="R23" t="n">
-        <v>7215856</v>
+        <v>7216002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020033</v>
+        <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,42 +2847,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723480</v>
+        <v>723341</v>
       </c>
       <c r="R24" t="n">
-        <v>7215979</v>
+        <v>7215856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,11 +2907,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020093</v>
+        <v>127020016</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723104</v>
+        <v>723237</v>
       </c>
       <c r="R25" t="n">
-        <v>7215946</v>
+        <v>7216401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3043,10 +3030,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020016</v>
+        <v>127020033</v>
       </c>
       <c r="B26" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,34 +3041,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723237</v>
+        <v>723480</v>
       </c>
       <c r="R26" t="n">
-        <v>7216401</v>
+        <v>7215979</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,6 +3109,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,46 +3151,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R27" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,17 +3213,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,34 +3249,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R28" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,13 +3323,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3352,53 +3352,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020049</v>
+        <v>127020080</v>
       </c>
       <c r="B29" t="n">
-        <v>56849</v>
+        <v>78772</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723659</v>
+        <v>723686</v>
       </c>
       <c r="R29" t="n">
-        <v>7216289</v>
+        <v>7216284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3431,11 +3423,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3462,32 +3449,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020057</v>
+        <v>127020081</v>
       </c>
       <c r="B30" t="n">
-        <v>98464</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723541</v>
+        <v>723396</v>
       </c>
       <c r="R30" t="n">
-        <v>7216191</v>
+        <v>7215995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020081</v>
+        <v>127020117</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>78420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3570,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3594,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723396</v>
+        <v>723317</v>
       </c>
       <c r="R31" t="n">
-        <v>7215995</v>
+        <v>7216136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,45 +3643,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020080</v>
+        <v>127020049</v>
       </c>
       <c r="B32" t="n">
-        <v>78772</v>
+        <v>56849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723686</v>
+        <v>723659</v>
       </c>
       <c r="R32" t="n">
-        <v>7216284</v>
+        <v>7216289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,6 +3722,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,32 +3753,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020117</v>
+        <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>78420</v>
+        <v>98464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723317</v>
+        <v>723541</v>
       </c>
       <c r="R33" t="n">
-        <v>7216136</v>
+        <v>7216191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020060</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57654</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723333</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7216135</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020017</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,34 +4055,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723183</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7216366</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020111</v>
+        <v>127020112</v>
       </c>
       <c r="B45" t="n">
         <v>92616</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723538</v>
+        <v>723697</v>
       </c>
       <c r="R45" t="n">
-        <v>7216303</v>
+        <v>7216227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020112</v>
+        <v>127020111</v>
       </c>
       <c r="B46" t="n">
         <v>92616</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723697</v>
+        <v>723538</v>
       </c>
       <c r="R46" t="n">
-        <v>7216227</v>
+        <v>7216303</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020056</v>
+        <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,42 +5188,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723286</v>
+        <v>723587</v>
       </c>
       <c r="R47" t="n">
-        <v>7216268</v>
+        <v>7216223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5256,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020024</v>
+        <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,34 +5285,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723587</v>
+        <v>723273</v>
       </c>
       <c r="R48" t="n">
-        <v>7216223</v>
+        <v>7216111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5353,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020027</v>
+        <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723273</v>
+        <v>723286</v>
       </c>
       <c r="R49" t="n">
-        <v>7216111</v>
+        <v>7216268</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>78773</v>
+        <v>57817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,34 +5505,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R50" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,13 +5575,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5701,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020053</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>78773</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5700,42 +5712,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723526</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7216153</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5770,17 +5774,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Lock</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020073</v>
       </c>
       <c r="B53" t="n">
-        <v>91587</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723348</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7215836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5878,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5896,32 +5897,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>82855</v>
+        <v>91587</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5932,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,10 +5994,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6004,21 +6005,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6091,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6187,32 +6188,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>127020110</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6222,10 +6223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723323</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216249</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6266,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B60" t="n">
-        <v>57761</v>
+        <v>78773</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R60" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,6 +6571,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6589,10 +6590,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020069</v>
+        <v>127020058</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6600,34 +6601,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723237</v>
+        <v>723561</v>
       </c>
       <c r="R61" t="n">
-        <v>7216401</v>
+        <v>7216205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,13 +6671,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6687,27 +6700,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020058</v>
+        <v>127020076</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>57761</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6716,24 +6729,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723561</v>
+        <v>723707</v>
       </c>
       <c r="R62" t="n">
-        <v>7216205</v>
+        <v>7216227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B63" t="n">
-        <v>57817</v>
+        <v>90361</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,42 +6808,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R63" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6876,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6907,10 +6894,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020020</v>
+        <v>127020055</v>
       </c>
       <c r="B64" t="n">
-        <v>90361</v>
+        <v>57817</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6918,34 +6905,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723341</v>
+        <v>723650</v>
       </c>
       <c r="R64" t="n">
-        <v>7216126</v>
+        <v>7216234</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6978,6 +6973,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020109</v>
+        <v>127020018</v>
       </c>
       <c r="B16" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723233</v>
+        <v>723548</v>
       </c>
       <c r="R16" t="n">
-        <v>7216428</v>
+        <v>7215979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R17" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020018</v>
+        <v>127020098</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723548</v>
+        <v>723581</v>
       </c>
       <c r="R18" t="n">
-        <v>7215979</v>
+        <v>7216130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,42 +4483,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R40" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,11 +4543,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4582,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,21 +4580,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4617,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R41" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4679,10 +4666,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,34 +4677,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R42" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4750,6 +4745,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020056</v>
       </c>
       <c r="B47" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,34 +5188,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723286</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216268</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5256,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91326</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,42 +5298,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5353,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020056</v>
+        <v>127020027</v>
       </c>
       <c r="B49" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723286</v>
+        <v>723273</v>
       </c>
       <c r="R49" t="n">
-        <v>7216268</v>
+        <v>7216111</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020073</v>
+        <v>127020105</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>82855</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723348</v>
+        <v>723580</v>
       </c>
       <c r="R53" t="n">
-        <v>7215836</v>
+        <v>7216146</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,7 +5878,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5897,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5932,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5994,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020110</v>
       </c>
       <c r="B55" t="n">
-        <v>82855</v>
+        <v>92616</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723323</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216249</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6091,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020107</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6126,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723230</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7216412</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,32 +6187,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020110</v>
+        <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6223,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723323</v>
+        <v>723348</v>
       </c>
       <c r="R57" t="n">
-        <v>7216249</v>
+        <v>7215836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020069</v>
+        <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6503,34 +6503,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723237</v>
+        <v>723561</v>
       </c>
       <c r="R60" t="n">
-        <v>7216401</v>
+        <v>7216205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,13 +6573,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6590,10 +6602,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020058</v>
+        <v>127020069</v>
       </c>
       <c r="B61" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6601,42 +6613,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723561</v>
+        <v>723237</v>
       </c>
       <c r="R61" t="n">
-        <v>7216205</v>
+        <v>7216401</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6671,17 +6675,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020018</v>
+        <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723548</v>
+        <v>723233</v>
       </c>
       <c r="R16" t="n">
-        <v>7215979</v>
+        <v>7216428</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>127020098</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723581</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7216130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020098</v>
+        <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723581</v>
+        <v>723548</v>
       </c>
       <c r="R18" t="n">
-        <v>7216130</v>
+        <v>7215979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020093</v>
+        <v>127020101</v>
       </c>
       <c r="B22" t="n">
         <v>79014</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723104</v>
+        <v>723341</v>
       </c>
       <c r="R22" t="n">
-        <v>7215946</v>
+        <v>7215856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020067</v>
+        <v>127020016</v>
       </c>
       <c r="B23" t="n">
-        <v>92809</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723414</v>
+        <v>723237</v>
       </c>
       <c r="R23" t="n">
-        <v>7216002</v>
+        <v>7216401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020067</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723414</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7216002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020016</v>
+        <v>127020093</v>
       </c>
       <c r="B25" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723237</v>
+        <v>723104</v>
       </c>
       <c r="R25" t="n">
-        <v>7216401</v>
+        <v>7215946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,34 +3151,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R27" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,13 +3225,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,46 +3265,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R28" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,17 +3327,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3352,32 +3352,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020080</v>
+        <v>127020057</v>
       </c>
       <c r="B29" t="n">
-        <v>78772</v>
+        <v>98464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723686</v>
+        <v>723541</v>
       </c>
       <c r="R29" t="n">
-        <v>7216284</v>
+        <v>7216191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020081</v>
+        <v>127020080</v>
       </c>
       <c r="B30" t="n">
         <v>78772</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723396</v>
+        <v>723686</v>
       </c>
       <c r="R30" t="n">
-        <v>7215995</v>
+        <v>7216284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020117</v>
+        <v>127020081</v>
       </c>
       <c r="B31" t="n">
-        <v>78420</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723317</v>
+        <v>723396</v>
       </c>
       <c r="R31" t="n">
-        <v>7216136</v>
+        <v>7215995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,53 +3643,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020049</v>
+        <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>78420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723659</v>
+        <v>723317</v>
       </c>
       <c r="R32" t="n">
-        <v>7216289</v>
+        <v>7216136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3722,11 +3714,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,10 +3740,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020057</v>
+        <v>127020049</v>
       </c>
       <c r="B33" t="n">
-        <v>98464</v>
+        <v>56849</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3764,34 +3751,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723541</v>
+        <v>723659</v>
       </c>
       <c r="R33" t="n">
-        <v>7216191</v>
+        <v>7216289</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,6 +3819,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,16 +4068,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4077,7 +4090,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4087,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4127,7 +4140,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,10 +4167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,42 +4178,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4233,11 +4238,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5799,10 +5799,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020105</v>
+        <v>127020073</v>
       </c>
       <c r="B53" t="n">
-        <v>82855</v>
+        <v>78773</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5810,21 +5810,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723580</v>
+        <v>723348</v>
       </c>
       <c r="R53" t="n">
-        <v>7216146</v>
+        <v>7215836</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,6 +5878,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5896,32 +5897,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020097</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5932,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723576</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216143</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5994,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020110</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>92616</v>
+        <v>82855</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6029,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723323</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216249</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6091,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6126,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6187,32 +6188,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>127020110</v>
       </c>
       <c r="B57" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6222,10 +6223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723323</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216249</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6266,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020094</v>
+        <v>127020035</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,34 +6296,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723509</v>
+        <v>723333</v>
       </c>
       <c r="R58" t="n">
-        <v>7216058</v>
+        <v>7215846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6350,12 +6358,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6382,10 +6395,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020035</v>
+        <v>127020094</v>
       </c>
       <c r="B59" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6393,42 +6406,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723333</v>
+        <v>723509</v>
       </c>
       <c r="R59" t="n">
-        <v>7215846</v>
+        <v>7216058</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,17 +6460,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91684</v>
+        <v>91688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020109</v>
+        <v>127020018</v>
       </c>
       <c r="B16" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723233</v>
+        <v>723548</v>
       </c>
       <c r="R16" t="n">
-        <v>7216428</v>
+        <v>7215979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R17" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020018</v>
+        <v>127020098</v>
       </c>
       <c r="B18" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723548</v>
+        <v>723581</v>
       </c>
       <c r="R18" t="n">
-        <v>7215979</v>
+        <v>7216130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,6 +2417,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2443,10 +2448,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>92624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2454,21 +2459,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R20" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,11 +2519,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2545,32 +2545,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R21" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020101</v>
+        <v>127020067</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>92813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723341</v>
+        <v>723414</v>
       </c>
       <c r="R22" t="n">
-        <v>7215856</v>
+        <v>7216002</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020016</v>
+        <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723237</v>
+        <v>723104</v>
       </c>
       <c r="R23" t="n">
-        <v>7216401</v>
+        <v>7215946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020067</v>
+        <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>92809</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723414</v>
+        <v>723341</v>
       </c>
       <c r="R24" t="n">
-        <v>7216002</v>
+        <v>7215856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020093</v>
+        <v>127020016</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723104</v>
+        <v>723237</v>
       </c>
       <c r="R25" t="n">
-        <v>7215946</v>
+        <v>7216401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
         <v>127020033</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,32 +3352,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020057</v>
+        <v>127020080</v>
       </c>
       <c r="B29" t="n">
-        <v>98464</v>
+        <v>78776</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723541</v>
+        <v>723686</v>
       </c>
       <c r="R29" t="n">
-        <v>7216191</v>
+        <v>7216284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020080</v>
+        <v>127020117</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>78424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3460,21 +3460,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723686</v>
+        <v>723317</v>
       </c>
       <c r="R30" t="n">
-        <v>7216284</v>
+        <v>7216136</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3549,7 +3549,7 @@
         <v>127020081</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020117</v>
+        <v>127020057</v>
       </c>
       <c r="B32" t="n">
-        <v>78420</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723317</v>
+        <v>723541</v>
       </c>
       <c r="R32" t="n">
-        <v>7216136</v>
+        <v>7216191</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3743,7 +3743,7 @@
         <v>127020049</v>
       </c>
       <c r="B33" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92620</v>
+        <v>92624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4090,7 +4077,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4100,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4167,10 +4154,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>79632</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,34 +4165,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4238,6 +4233,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57654</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4377,7 +4377,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
         <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>127020112</v>
       </c>
       <c r="B45" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>127020111</v>
       </c>
       <c r="B46" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020056</v>
+        <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>57817</v>
+        <v>91330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,42 +5188,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723286</v>
+        <v>723587</v>
       </c>
       <c r="R47" t="n">
-        <v>7216268</v>
+        <v>7216223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5256,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020024</v>
+        <v>127020056</v>
       </c>
       <c r="B48" t="n">
-        <v>91326</v>
+        <v>57821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,34 +5285,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723587</v>
+        <v>723286</v>
       </c>
       <c r="R48" t="n">
-        <v>7216223</v>
+        <v>7216268</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5353,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5387,7 +5387,7 @@
         <v>127020027</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>127020082</v>
       </c>
       <c r="B51" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020073</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>78773</v>
+        <v>91591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723348</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7215836</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5878,7 +5878,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5897,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>91587</v>
+        <v>82859</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5932,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5994,10 +5993,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020097</v>
       </c>
       <c r="B55" t="n">
-        <v>82855</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6005,21 +6004,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6029,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723576</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216143</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6091,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6126,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723323</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7216249</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6188,32 +6187,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020110</v>
+        <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>92616</v>
+        <v>78777</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6223,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723323</v>
+        <v>723348</v>
       </c>
       <c r="R57" t="n">
-        <v>7216249</v>
+        <v>7215836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020035</v>
+        <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,42 +6296,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723333</v>
+        <v>723509</v>
       </c>
       <c r="R58" t="n">
-        <v>7215846</v>
+        <v>7216058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,17 +6350,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6395,10 +6382,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020094</v>
+        <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,34 +6393,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723509</v>
+        <v>723333</v>
       </c>
       <c r="R59" t="n">
-        <v>7216058</v>
+        <v>7215846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6460,12 +6455,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6492,27 +6492,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020058</v>
+        <v>127020076</v>
       </c>
       <c r="B60" t="n">
-        <v>57654</v>
+        <v>57765</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6521,24 +6521,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723561</v>
+        <v>723707</v>
       </c>
       <c r="R60" t="n">
-        <v>7216205</v>
+        <v>7216227</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,11 +6563,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6605,7 +6592,7 @@
         <v>127020069</v>
       </c>
       <c r="B61" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6700,27 +6687,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020076</v>
+        <v>127020058</v>
       </c>
       <c r="B62" t="n">
-        <v>57761</v>
+        <v>57658</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6729,16 +6716,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723707</v>
+        <v>723561</v>
       </c>
       <c r="R62" t="n">
-        <v>7216227</v>
+        <v>7216205</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6771,6 +6766,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020020</v>
+        <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>90361</v>
+        <v>57821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,34 +6808,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723341</v>
+        <v>723650</v>
       </c>
       <c r="R63" t="n">
-        <v>7216126</v>
+        <v>7216234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6876,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,10 +6907,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>57817</v>
+        <v>90365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6905,42 +6918,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R64" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,11 +6978,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7007,7 +7007,7 @@
         <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1654,32 +1654,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B12" t="n">
-        <v>91688</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R12" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020068</v>
+        <v>127020059</v>
       </c>
       <c r="B13" t="n">
-        <v>92813</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,34 +1762,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723341</v>
+        <v>723530</v>
       </c>
       <c r="R13" t="n">
-        <v>7215856</v>
+        <v>7216208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1822,6 +1830,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1848,32 +1861,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020095</v>
+        <v>127020023</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>91688</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723589</v>
+        <v>723592</v>
       </c>
       <c r="R14" t="n">
-        <v>7216289</v>
+        <v>7216220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1958,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020059</v>
+        <v>127020068</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>92813</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,42 +1969,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723530</v>
+        <v>723341</v>
       </c>
       <c r="R15" t="n">
-        <v>7216208</v>
+        <v>7215856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2024,11 +2029,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>127020098</v>
       </c>
       <c r="B17" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723581</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7216130</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2249,32 +2249,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R18" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,32 +2540,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R21" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020067</v>
+        <v>127020016</v>
       </c>
       <c r="B22" t="n">
-        <v>92813</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723414</v>
+        <v>723237</v>
       </c>
       <c r="R22" t="n">
-        <v>7216002</v>
+        <v>7216401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>92813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,21 +2944,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R25" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3449,10 +3449,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020117</v>
+        <v>127020081</v>
       </c>
       <c r="B30" t="n">
-        <v>78424</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3460,21 +3460,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723317</v>
+        <v>723396</v>
       </c>
       <c r="R30" t="n">
-        <v>7216136</v>
+        <v>7215995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020081</v>
+        <v>127020117</v>
       </c>
       <c r="B31" t="n">
-        <v>78776</v>
+        <v>78424</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723396</v>
+        <v>723317</v>
       </c>
       <c r="R31" t="n">
-        <v>7215995</v>
+        <v>7216136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B36" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,16 +4068,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4077,7 +4090,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4087,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4127,7 +4140,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,10 +4167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,42 +4178,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4233,11 +4238,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,34 +4483,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R40" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4543,6 +4551,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4569,10 +4582,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,21 +4593,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4617,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R41" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4666,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,42 +4690,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R42" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4745,11 +4750,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020112</v>
+        <v>127020111</v>
       </c>
       <c r="B45" t="n">
         <v>92620</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723697</v>
+        <v>723538</v>
       </c>
       <c r="R45" t="n">
-        <v>7216227</v>
+        <v>7216303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020111</v>
+        <v>127020112</v>
       </c>
       <c r="B46" t="n">
         <v>92620</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723538</v>
+        <v>723697</v>
       </c>
       <c r="R46" t="n">
-        <v>7216303</v>
+        <v>7216227</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020056</v>
+        <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723286</v>
+        <v>723273</v>
       </c>
       <c r="R48" t="n">
-        <v>7216268</v>
+        <v>7216111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020027</v>
+        <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723273</v>
+        <v>723286</v>
       </c>
       <c r="R49" t="n">
-        <v>7216111</v>
+        <v>7216268</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R51" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5683,6 +5683,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5702,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020070</v>
+        <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,21 +5713,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5736,10 +5737,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723330</v>
+        <v>723348</v>
       </c>
       <c r="R52" t="n">
-        <v>7216136</v>
+        <v>7215836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5780,7 +5781,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B53" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020110</v>
       </c>
       <c r="B54" t="n">
-        <v>82859</v>
+        <v>92620</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723323</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216249</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020110</v>
+        <v>127020107</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>91591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723323</v>
+        <v>723230</v>
       </c>
       <c r="R56" t="n">
-        <v>7216249</v>
+        <v>7216412</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6492,32 +6492,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B60" t="n">
-        <v>57765</v>
+        <v>78777</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6527,10 +6527,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R60" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6571,6 +6571,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6589,10 +6590,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020069</v>
+        <v>127020058</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6600,34 +6601,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723237</v>
+        <v>723561</v>
       </c>
       <c r="R61" t="n">
-        <v>7216401</v>
+        <v>7216205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,13 +6671,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6687,27 +6700,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020058</v>
+        <v>127020076</v>
       </c>
       <c r="B62" t="n">
-        <v>57658</v>
+        <v>57765</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6716,24 +6729,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723561</v>
+        <v>723707</v>
       </c>
       <c r="R62" t="n">
-        <v>7216205</v>
+        <v>7216227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6766,11 +6771,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6797,53 +6797,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020055</v>
+        <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723650</v>
+        <v>723260</v>
       </c>
       <c r="R63" t="n">
-        <v>7216234</v>
+        <v>7216304</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6880,7 +6872,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,45 +6996,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R65" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2739,7 +2739,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020093</v>
+        <v>127020101</v>
       </c>
       <c r="B23" t="n">
         <v>79018</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723104</v>
+        <v>723341</v>
       </c>
       <c r="R23" t="n">
-        <v>7215946</v>
+        <v>7215856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020067</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723414</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7216002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020067</v>
+        <v>127020033</v>
       </c>
       <c r="B25" t="n">
-        <v>92813</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,34 +2944,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723414</v>
+        <v>723480</v>
       </c>
       <c r="R25" t="n">
-        <v>7216002</v>
+        <v>7215979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3004,6 +3012,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3030,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020033</v>
+        <v>127020093</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3041,42 +3054,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723480</v>
+        <v>723104</v>
       </c>
       <c r="R26" t="n">
-        <v>7215979</v>
+        <v>7215946</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,11 +3114,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,46 +3151,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R27" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,17 +3213,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,34 +3249,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R28" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,13 +3323,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3546,45 +3546,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020117</v>
+        <v>127020049</v>
       </c>
       <c r="B31" t="n">
-        <v>78424</v>
+        <v>56853</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723317</v>
+        <v>723659</v>
       </c>
       <c r="R31" t="n">
-        <v>7216136</v>
+        <v>7216289</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3617,6 +3625,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3740,53 +3753,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020049</v>
+        <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>78424</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723659</v>
+        <v>723317</v>
       </c>
       <c r="R33" t="n">
-        <v>7216289</v>
+        <v>7216136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,11 +3824,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4090,7 +4077,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4100,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4167,10 +4154,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,34 +4165,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4238,6 +4233,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5274,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020056</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723286</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216268</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020056</v>
+        <v>127020027</v>
       </c>
       <c r="B49" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723286</v>
+        <v>723273</v>
       </c>
       <c r="R49" t="n">
-        <v>7216268</v>
+        <v>7216111</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,6 +2417,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2443,32 +2448,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>92624</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R20" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2540,10 +2545,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>92624</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2551,21 +2556,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2611,11 +2616,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,34 +3151,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R27" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,13 +3225,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,46 +3265,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R28" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,17 +3327,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3546,53 +3546,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020049</v>
+        <v>127020117</v>
       </c>
       <c r="B31" t="n">
-        <v>56853</v>
+        <v>78424</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723659</v>
+        <v>723317</v>
       </c>
       <c r="R31" t="n">
-        <v>7216289</v>
+        <v>7216136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3625,11 +3617,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3753,45 +3740,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020117</v>
+        <v>127020049</v>
       </c>
       <c r="B33" t="n">
-        <v>78424</v>
+        <v>56853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723317</v>
+        <v>723659</v>
       </c>
       <c r="R33" t="n">
-        <v>7216136</v>
+        <v>7216289</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,6 +3819,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,42 +4483,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R40" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,11 +4543,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4582,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,34 +4580,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R41" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,6 +4648,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R42" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020056</v>
+        <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57821</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,21 +5285,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5307,7 +5307,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723286</v>
+        <v>723273</v>
       </c>
       <c r="R48" t="n">
-        <v>7216268</v>
+        <v>7216111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020027</v>
+        <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57821</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5417,7 +5417,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5427,10 +5427,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723273</v>
+        <v>723286</v>
       </c>
       <c r="R49" t="n">
-        <v>7216111</v>
+        <v>7216268</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020095</v>
+        <v>127020059</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723589</v>
+        <v>723530</v>
       </c>
       <c r="R12" t="n">
-        <v>7216289</v>
+        <v>7216208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1725,6 +1733,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1751,53 +1764,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020059</v>
+        <v>127020023</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>91688</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723530</v>
+        <v>723592</v>
       </c>
       <c r="R13" t="n">
-        <v>7216208</v>
+        <v>7216220</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1830,11 +1835,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1861,32 +1861,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020023</v>
+        <v>127020068</v>
       </c>
       <c r="B14" t="n">
-        <v>91688</v>
+        <v>92813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723592</v>
+        <v>723341</v>
       </c>
       <c r="R14" t="n">
-        <v>7216220</v>
+        <v>7215856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,10 +1958,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020068</v>
+        <v>127020095</v>
       </c>
       <c r="B15" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723341</v>
+        <v>723589</v>
       </c>
       <c r="R15" t="n">
-        <v>7215856</v>
+        <v>7216289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>98447</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2448,32 +2443,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2483,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R20" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2519,6 +2514,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,7 +2739,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020101</v>
+        <v>127020093</v>
       </c>
       <c r="B23" t="n">
         <v>79018</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723341</v>
+        <v>723104</v>
       </c>
       <c r="R23" t="n">
-        <v>7215856</v>
+        <v>7215946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020067</v>
+        <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,21 +2847,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723414</v>
+        <v>723341</v>
       </c>
       <c r="R24" t="n">
-        <v>7216002</v>
+        <v>7215856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020033</v>
+        <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>92813</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2944,42 +2944,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723480</v>
+        <v>723414</v>
       </c>
       <c r="R25" t="n">
-        <v>7215979</v>
+        <v>7216002</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,11 +3004,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3043,10 +3030,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020093</v>
+        <v>127020033</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,34 +3041,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723104</v>
+        <v>723480</v>
       </c>
       <c r="R26" t="n">
-        <v>7215946</v>
+        <v>7215979</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3114,6 +3109,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3352,32 +3352,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020080</v>
+        <v>127020057</v>
       </c>
       <c r="B29" t="n">
-        <v>78776</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723686</v>
+        <v>723541</v>
       </c>
       <c r="R29" t="n">
-        <v>7216284</v>
+        <v>7216191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020081</v>
+        <v>127020080</v>
       </c>
       <c r="B30" t="n">
         <v>78776</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723396</v>
+        <v>723686</v>
       </c>
       <c r="R30" t="n">
-        <v>7215995</v>
+        <v>7216284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020117</v>
+        <v>127020081</v>
       </c>
       <c r="B31" t="n">
-        <v>78424</v>
+        <v>78776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723317</v>
+        <v>723396</v>
       </c>
       <c r="R31" t="n">
-        <v>7216136</v>
+        <v>7215995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,32 +3643,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020057</v>
+        <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>78424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723541</v>
+        <v>723317</v>
       </c>
       <c r="R32" t="n">
-        <v>7216191</v>
+        <v>7216136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B36" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,16 +4068,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4077,7 +4090,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4087,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4127,7 +4140,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,10 +4167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,42 +4178,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4233,11 +4238,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>127020031</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,34 +4483,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723592</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7216060</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4543,6 +4551,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4569,10 +4582,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020031</v>
+        <v>127020019</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,42 +4593,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723592</v>
+        <v>723486</v>
       </c>
       <c r="R41" t="n">
-        <v>7216060</v>
+        <v>7215989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4648,11 +4653,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B42" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4714,10 +4714,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R42" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020027</v>
       </c>
       <c r="B47" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,34 +5188,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723273</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216111</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5256,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5285,42 +5298,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5353,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020053</v>
+        <v>127020082</v>
       </c>
       <c r="B50" t="n">
-        <v>57821</v>
+        <v>78776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,42 +5505,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723526</v>
+        <v>723348</v>
       </c>
       <c r="R50" t="n">
-        <v>7216153</v>
+        <v>7215836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020070</v>
+        <v>127020053</v>
       </c>
       <c r="B51" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5615,34 +5602,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723330</v>
+        <v>723526</v>
       </c>
       <c r="R51" t="n">
-        <v>7216136</v>
+        <v>7216153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5677,13 +5672,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5702,10 +5701,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,21 +5712,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5737,10 +5736,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,6 +5780,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020097</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723576</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7216143</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020110</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>92620</v>
+        <v>82859</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723323</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216249</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020110</v>
       </c>
       <c r="B55" t="n">
-        <v>82859</v>
+        <v>92620</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723323</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216249</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6492,10 +6492,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020069</v>
+        <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6503,34 +6503,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723237</v>
+        <v>723561</v>
       </c>
       <c r="R60" t="n">
-        <v>7216401</v>
+        <v>7216205</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,13 +6573,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6590,27 +6602,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020058</v>
+        <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57658</v>
+        <v>57765</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6619,24 +6631,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723561</v>
+        <v>723707</v>
       </c>
       <c r="R61" t="n">
-        <v>7216205</v>
+        <v>7216227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6669,11 +6673,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6700,32 +6699,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>57765</v>
+        <v>78777</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6734,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R62" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6779,6 +6778,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6797,45 +6797,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>98447</v>
+        <v>57821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R63" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6872,7 +6880,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,32 +6907,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020020</v>
+        <v>127020084</v>
       </c>
       <c r="B64" t="n">
-        <v>90365</v>
+        <v>98448</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6934,10 +6942,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723341</v>
+        <v>723260</v>
       </c>
       <c r="R64" t="n">
-        <v>7216126</v>
+        <v>7216304</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6970,6 +6978,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6996,10 +7009,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B65" t="n">
-        <v>57821</v>
+        <v>90365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7007,42 +7020,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7075,11 +7080,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>92624</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723192</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216368</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,32 +2545,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B21" t="n">
-        <v>92624</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R21" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B27" t="n">
-        <v>57661</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,46 +3151,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R27" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,17 +3213,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,10 +3238,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,34 +3249,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R28" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,13 +3323,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020031</v>
+        <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,42 +4483,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723592</v>
+        <v>723486</v>
       </c>
       <c r="R40" t="n">
-        <v>7216060</v>
+        <v>7215989</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,11 +4543,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4582,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4593,21 +4580,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4617,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4679,10 +4666,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020096</v>
+        <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,34 +4677,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723595</v>
+        <v>723592</v>
       </c>
       <c r="R42" t="n">
-        <v>7216276</v>
+        <v>7216060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4750,6 +4745,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4776,45 +4776,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R43" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,6 +4855,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4873,53 +4886,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B44" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R44" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4952,11 +4957,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020027</v>
+        <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>91330</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,42 +5188,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723273</v>
+        <v>723587</v>
       </c>
       <c r="R47" t="n">
-        <v>7216111</v>
+        <v>7216223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5256,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020024</v>
+        <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>91330</v>
+        <v>57661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,34 +5285,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723587</v>
+        <v>723273</v>
       </c>
       <c r="R48" t="n">
-        <v>7216223</v>
+        <v>7216111</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5353,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6602,32 +6602,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B61" t="n">
-        <v>57765</v>
+        <v>78777</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R61" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,6 +6681,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6699,32 +6700,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B62" t="n">
-        <v>78777</v>
+        <v>57765</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6734,10 +6735,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R62" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6778,7 +6779,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020059</v>
+        <v>127020095</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,42 +1665,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723530</v>
+        <v>723589</v>
       </c>
       <c r="R12" t="n">
-        <v>7216208</v>
+        <v>7216289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1733,11 +1725,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,7 +1754,7 @@
         <v>127020023</v>
       </c>
       <c r="B13" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1864,7 +1851,7 @@
         <v>127020068</v>
       </c>
       <c r="B14" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020095</v>
+        <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,34 +1956,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723589</v>
+        <v>723530</v>
       </c>
       <c r="R15" t="n">
-        <v>7216289</v>
+        <v>7216208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,6 +2024,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020018</v>
+        <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723548</v>
+        <v>723233</v>
       </c>
       <c r="R16" t="n">
-        <v>7215979</v>
+        <v>7216428</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2155,7 +2155,7 @@
         <v>127020098</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,32 +2249,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020109</v>
+        <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723233</v>
+        <v>723548</v>
       </c>
       <c r="R18" t="n">
-        <v>7216428</v>
+        <v>7215979</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>92624</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,10 +2443,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>92626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R20" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2514,11 +2514,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2545,32 +2540,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R21" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020016</v>
+        <v>127020101</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723237</v>
+        <v>723341</v>
       </c>
       <c r="R22" t="n">
-        <v>7216401</v>
+        <v>7215856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,7 +2742,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020033</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,34 +2847,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723480</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7215979</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2907,6 +2915,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2936,7 +2949,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3030,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020033</v>
+        <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>57661</v>
+        <v>79638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3041,42 +3054,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723480</v>
+        <v>723237</v>
       </c>
       <c r="R26" t="n">
-        <v>7215979</v>
+        <v>7216401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,11 +3114,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3143,7 +3143,7 @@
         <v>127020072</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>127020029</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,32 +3352,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020057</v>
+        <v>127020081</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>78778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723541</v>
+        <v>723396</v>
       </c>
       <c r="R29" t="n">
-        <v>7216191</v>
+        <v>7215995</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3452,7 +3452,7 @@
         <v>127020080</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020081</v>
+        <v>127020117</v>
       </c>
       <c r="B31" t="n">
-        <v>78776</v>
+        <v>78426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3557,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723396</v>
+        <v>723317</v>
       </c>
       <c r="R31" t="n">
-        <v>7215995</v>
+        <v>7216136</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,45 +3643,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020117</v>
+        <v>127020049</v>
       </c>
       <c r="B32" t="n">
-        <v>78424</v>
+        <v>56855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723317</v>
+        <v>723659</v>
       </c>
       <c r="R32" t="n">
-        <v>7216136</v>
+        <v>7216289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3714,6 +3722,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3740,10 +3753,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020049</v>
+        <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>56853</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3751,42 +3764,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723659</v>
+        <v>723541</v>
       </c>
       <c r="R33" t="n">
-        <v>7216289</v>
+        <v>7216191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,11 +3824,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92624</v>
+        <v>92626</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127020026</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>127020032</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127020017</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>127020060</v>
       </c>
       <c r="B38" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R40" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020096</v>
+        <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,34 +4580,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723595</v>
+        <v>723592</v>
       </c>
       <c r="R41" t="n">
-        <v>7216276</v>
+        <v>7216060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4640,6 +4648,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4666,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020031</v>
+        <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>79638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,42 +4690,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723592</v>
+        <v>723486</v>
       </c>
       <c r="R42" t="n">
-        <v>7216060</v>
+        <v>7215989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4745,11 +4750,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4776,53 +4776,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R43" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,11 +4847,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,45 +4873,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>56855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R44" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4957,6 +4952,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4983,10 +4983,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020111</v>
+        <v>127020112</v>
       </c>
       <c r="B45" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723538</v>
+        <v>723697</v>
       </c>
       <c r="R45" t="n">
-        <v>7216303</v>
+        <v>7216227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5080,10 +5080,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020112</v>
+        <v>127020111</v>
       </c>
       <c r="B46" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723697</v>
+        <v>723538</v>
       </c>
       <c r="R46" t="n">
-        <v>7216227</v>
+        <v>7216303</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,7 +5180,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>127020082</v>
       </c>
       <c r="B50" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>127020053</v>
       </c>
       <c r="B51" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020110</v>
       </c>
       <c r="B53" t="n">
-        <v>91591</v>
+        <v>92622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723323</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7216249</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>82859</v>
+        <v>91593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020110</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>92620</v>
+        <v>82861</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723323</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216249</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020073</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6101,21 +6101,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723348</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7215836</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6169,6 +6169,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6187,10 +6188,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>127020097</v>
       </c>
       <c r="B57" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6198,21 +6199,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6222,10 +6223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723576</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216143</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6266,7 +6267,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020094</v>
+        <v>127020035</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,34 +6296,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723509</v>
+        <v>723333</v>
       </c>
       <c r="R58" t="n">
-        <v>7216058</v>
+        <v>7215846</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6350,12 +6358,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6382,10 +6395,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020035</v>
+        <v>127020094</v>
       </c>
       <c r="B59" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6393,42 +6406,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723333</v>
+        <v>723509</v>
       </c>
       <c r="R59" t="n">
-        <v>7215846</v>
+        <v>7216058</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,17 +6460,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6495,7 +6495,7 @@
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6602,32 +6602,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>78777</v>
+        <v>57767</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6637,10 +6637,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R61" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6681,7 +6681,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6700,32 +6699,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020076</v>
+        <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>57765</v>
+        <v>78779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,10 +6734,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R62" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6779,6 +6778,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>127020084</v>
       </c>
       <c r="B64" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>127020020</v>
       </c>
       <c r="B65" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7314,6 +7314,112 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>127735569</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>723602</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7216242</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>98450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,6 +2417,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2540,32 +2545,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>78778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2575,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2611,11 +2616,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020101</v>
+        <v>127020016</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723341</v>
+        <v>723237</v>
       </c>
       <c r="R22" t="n">
-        <v>7215856</v>
+        <v>7216401</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020093</v>
+        <v>127020033</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,34 +2750,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723104</v>
+        <v>723480</v>
       </c>
       <c r="R23" t="n">
-        <v>7215946</v>
+        <v>7215979</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2810,6 +2818,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2836,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020033</v>
+        <v>127020067</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>92815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2847,42 +2860,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723480</v>
+        <v>723414</v>
       </c>
       <c r="R24" t="n">
-        <v>7215979</v>
+        <v>7216002</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2915,11 +2920,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2946,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020067</v>
+        <v>127020093</v>
       </c>
       <c r="B25" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,21 +2957,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723414</v>
+        <v>723104</v>
       </c>
       <c r="R25" t="n">
-        <v>7216002</v>
+        <v>7215946</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020016</v>
+        <v>127020101</v>
       </c>
       <c r="B26" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723237</v>
+        <v>723341</v>
       </c>
       <c r="R26" t="n">
-        <v>7216401</v>
+        <v>7215856</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020081</v>
+        <v>127020080</v>
       </c>
       <c r="B29" t="n">
         <v>78778</v>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723396</v>
+        <v>723686</v>
       </c>
       <c r="R29" t="n">
-        <v>7215995</v>
+        <v>7216284</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020080</v>
+        <v>127020081</v>
       </c>
       <c r="B30" t="n">
         <v>78778</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723686</v>
+        <v>723396</v>
       </c>
       <c r="R30" t="n">
-        <v>7216284</v>
+        <v>7215995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020032</v>
+        <v>127020060</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,16 +4055,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4090,7 +4077,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4100,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723539</v>
+        <v>723333</v>
       </c>
       <c r="R36" t="n">
-        <v>7215974</v>
+        <v>7216135</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4140,7 +4127,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4167,10 +4154,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,34 +4165,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4238,6 +4233,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020060</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,16 +4275,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723333</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216135</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,42 +4580,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4648,11 +4640,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4679,10 +4666,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4690,34 +4677,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R42" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4750,6 +4745,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4983,7 +4983,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020112</v>
+        <v>127020111</v>
       </c>
       <c r="B45" t="n">
         <v>92622</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723697</v>
+        <v>723538</v>
       </c>
       <c r="R45" t="n">
-        <v>7216227</v>
+        <v>7216303</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020111</v>
+        <v>127020112</v>
       </c>
       <c r="B46" t="n">
         <v>92622</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723538</v>
+        <v>723697</v>
       </c>
       <c r="R46" t="n">
-        <v>7216303</v>
+        <v>7216227</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020082</v>
+        <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>78778</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,34 +5505,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723348</v>
+        <v>723526</v>
       </c>
       <c r="R50" t="n">
-        <v>7215836</v>
+        <v>7216153</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,6 +5573,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5591,10 +5604,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020053</v>
+        <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>78779</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,42 +5615,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723526</v>
+        <v>723330</v>
       </c>
       <c r="R51" t="n">
-        <v>7216153</v>
+        <v>7216136</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,17 +5677,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lock</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5702,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020070</v>
+        <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,21 +5713,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5736,10 +5737,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723330</v>
+        <v>723348</v>
       </c>
       <c r="R52" t="n">
-        <v>7216136</v>
+        <v>7215836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5780,7 +5781,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>91593</v>
+        <v>82861</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B55" t="n">
-        <v>82861</v>
+        <v>91593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020073</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6101,21 +6101,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723348</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7215836</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6169,7 +6169,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6188,10 +6187,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020097</v>
+        <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6199,21 +6198,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6223,10 +6222,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723576</v>
+        <v>723348</v>
       </c>
       <c r="R57" t="n">
-        <v>7216143</v>
+        <v>7215836</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6267,6 +6266,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6285,10 +6285,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020035</v>
+        <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6296,42 +6296,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723333</v>
+        <v>723509</v>
       </c>
       <c r="R58" t="n">
-        <v>7215846</v>
+        <v>7216058</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,17 +6350,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6395,10 +6382,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020094</v>
+        <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,34 +6393,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723509</v>
+        <v>723333</v>
       </c>
       <c r="R59" t="n">
-        <v>7216058</v>
+        <v>7215846</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6460,12 +6455,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6797,10 +6797,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B63" t="n">
-        <v>57823</v>
+        <v>90367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6808,42 +6808,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R63" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6876,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6907,45 +6894,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B64" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R64" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6982,7 +6977,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7009,32 +7004,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020020</v>
+        <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>90367</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7044,10 +7039,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723341</v>
+        <v>723260</v>
       </c>
       <c r="R65" t="n">
-        <v>7216126</v>
+        <v>7216304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7080,6 +7075,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7106,10 +7106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127020099</v>
+        <v>127020030</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7117,34 +7117,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723570</v>
+        <v>723726</v>
       </c>
       <c r="R66" t="n">
-        <v>7216008</v>
+        <v>7216246</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7177,6 +7189,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7203,10 +7220,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127020030</v>
+        <v>127020099</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7214,46 +7231,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723726</v>
+        <v>723570</v>
       </c>
       <c r="R67" t="n">
-        <v>7216246</v>
+        <v>7216008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7286,11 +7291,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -3140,10 +3140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020072</v>
+        <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,34 +3151,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723485</v>
+        <v>723513</v>
       </c>
       <c r="R27" t="n">
-        <v>7216003</v>
+        <v>7216122</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,13 +3225,17 @@
           <t>2025-07-29</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hona, födosökande</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020029</v>
+        <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3249,46 +3265,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723513</v>
+        <v>723485</v>
       </c>
       <c r="R28" t="n">
-        <v>7216122</v>
+        <v>7216003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,17 +3327,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3352,45 +3352,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020080</v>
+        <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>78778</v>
+        <v>56855</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723686</v>
+        <v>723659</v>
       </c>
       <c r="R29" t="n">
-        <v>7216284</v>
+        <v>7216289</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3423,6 +3431,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3449,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020081</v>
+        <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>78778</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3484,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723396</v>
+        <v>723541</v>
       </c>
       <c r="R30" t="n">
-        <v>7215995</v>
+        <v>7216191</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,10 +3559,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020117</v>
+        <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78426</v>
+        <v>78778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,21 +3570,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3581,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723317</v>
+        <v>723686</v>
       </c>
       <c r="R31" t="n">
-        <v>7216136</v>
+        <v>7216284</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,53 +3656,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020049</v>
+        <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>56855</v>
+        <v>78778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723659</v>
+        <v>723396</v>
       </c>
       <c r="R32" t="n">
-        <v>7216289</v>
+        <v>7215995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3722,11 +3727,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,32 +3753,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020057</v>
+        <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>98471</v>
+        <v>78426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723541</v>
+        <v>723317</v>
       </c>
       <c r="R33" t="n">
-        <v>7216191</v>
+        <v>7216136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020032</v>
       </c>
       <c r="B35" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723539</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7215974</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020060</v>
+        <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,42 +4068,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723333</v>
+        <v>723183</v>
       </c>
       <c r="R36" t="n">
-        <v>7216135</v>
+        <v>7216366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,11 +4128,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020060</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723333</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7216135</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020026</v>
       </c>
       <c r="B38" t="n">
         <v>57663</v>
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723085</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216102</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4776,45 +4776,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R43" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,6 +4855,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4873,53 +4886,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B44" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R44" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4952,11 +4957,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020070</v>
+        <v>127020082</v>
       </c>
       <c r="B51" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5639,10 +5639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723330</v>
+        <v>723348</v>
       </c>
       <c r="R51" t="n">
-        <v>7216136</v>
+        <v>7215836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5683,7 +5683,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5702,10 +5701,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,21 +5712,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5737,10 +5736,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5781,6 +5780,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020020</v>
+        <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>90367</v>
+        <v>98450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723341</v>
+        <v>723260</v>
       </c>
       <c r="R63" t="n">
-        <v>7216126</v>
+        <v>7216304</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>90367</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6905,42 +6910,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R64" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,11 +6970,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7004,45 +6996,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R65" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7106,10 +7106,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127020030</v>
+        <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7117,46 +7117,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723726</v>
+        <v>723570</v>
       </c>
       <c r="R66" t="n">
-        <v>7216246</v>
+        <v>7216008</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7189,11 +7177,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7220,10 +7203,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127020099</v>
+        <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7231,34 +7214,46 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723570</v>
+        <v>723726</v>
       </c>
       <c r="R67" t="n">
-        <v>7216008</v>
+        <v>7216246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7291,6 +7286,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020095</v>
+        <v>127020059</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723589</v>
+        <v>723530</v>
       </c>
       <c r="R12" t="n">
-        <v>7216289</v>
+        <v>7216208</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1725,6 +1733,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1751,32 +1764,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B13" t="n">
-        <v>91690</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,10 +1799,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R13" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,32 +1861,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020068</v>
+        <v>127020023</v>
       </c>
       <c r="B14" t="n">
-        <v>92815</v>
+        <v>91690</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1896,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723341</v>
+        <v>723592</v>
       </c>
       <c r="R14" t="n">
-        <v>7215856</v>
+        <v>7216220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1958,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020059</v>
+        <v>127020068</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,42 +1969,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723530</v>
+        <v>723341</v>
       </c>
       <c r="R15" t="n">
-        <v>7216208</v>
+        <v>7215856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2024,11 +2029,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020083</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>98450</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723241</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216310</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2417,11 +2417,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2545,32 +2540,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>78778</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R21" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2611,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2642,10 +2642,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020016</v>
+        <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2653,34 +2653,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723237</v>
+        <v>723480</v>
       </c>
       <c r="R22" t="n">
-        <v>7216401</v>
+        <v>7215979</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2739,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020033</v>
+        <v>127020067</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>92815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2750,42 +2763,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723480</v>
+        <v>723414</v>
       </c>
       <c r="R23" t="n">
-        <v>7215979</v>
+        <v>7216002</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,11 +2823,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2849,10 +2849,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020067</v>
+        <v>127020093</v>
       </c>
       <c r="B24" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2860,21 +2860,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723414</v>
+        <v>723104</v>
       </c>
       <c r="R24" t="n">
-        <v>7216002</v>
+        <v>7215946</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020093</v>
+        <v>127020016</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,21 +2957,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723104</v>
+        <v>723237</v>
       </c>
       <c r="R25" t="n">
-        <v>7215946</v>
+        <v>7216401</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020057</v>
+        <v>127020080</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>78778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723541</v>
+        <v>723686</v>
       </c>
       <c r="R30" t="n">
-        <v>7216191</v>
+        <v>7216284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020080</v>
+        <v>127020081</v>
       </c>
       <c r="B31" t="n">
         <v>78778</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723686</v>
+        <v>723396</v>
       </c>
       <c r="R31" t="n">
-        <v>7216284</v>
+        <v>7215995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020081</v>
+        <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>78778</v>
+        <v>78426</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723396</v>
+        <v>723317</v>
       </c>
       <c r="R32" t="n">
-        <v>7215995</v>
+        <v>7216136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,32 +3753,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020117</v>
+        <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>78426</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723317</v>
+        <v>723541</v>
       </c>
       <c r="R33" t="n">
-        <v>7216136</v>
+        <v>7216191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020032</v>
+        <v>127020017</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,42 +3958,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723539</v>
+        <v>723183</v>
       </c>
       <c r="R35" t="n">
-        <v>7215974</v>
+        <v>7216366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,11 +4018,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4057,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B36" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,34 +4055,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R36" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020026</v>
+        <v>127020032</v>
       </c>
       <c r="B38" t="n">
         <v>57663</v>
@@ -4297,7 +4297,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723085</v>
+        <v>723539</v>
       </c>
       <c r="R38" t="n">
-        <v>7216102</v>
+        <v>7215974</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4472,10 +4472,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020019</v>
+        <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723486</v>
+        <v>723595</v>
       </c>
       <c r="R40" t="n">
-        <v>7215989</v>
+        <v>7216276</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,21 +4580,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R41" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020056</v>
       </c>
       <c r="B47" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,34 +5188,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723286</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216268</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5248,6 +5256,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5384,10 +5397,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020056</v>
+        <v>127020024</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>91332</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,42 +5408,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723286</v>
+        <v>723587</v>
       </c>
       <c r="R49" t="n">
-        <v>7216268</v>
+        <v>7216223</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5463,11 +5468,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020053</v>
+        <v>127020082</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>78778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,42 +5505,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723526</v>
+        <v>723348</v>
       </c>
       <c r="R50" t="n">
-        <v>7216153</v>
+        <v>7215836</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5573,11 +5565,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5604,10 +5591,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020082</v>
+        <v>127020053</v>
       </c>
       <c r="B51" t="n">
-        <v>78778</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5615,34 +5602,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723348</v>
+        <v>723526</v>
       </c>
       <c r="R51" t="n">
-        <v>7215836</v>
+        <v>7216153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,6 +5670,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B53" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R53" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020105</v>
+        <v>127020107</v>
       </c>
       <c r="B54" t="n">
-        <v>82861</v>
+        <v>91593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723580</v>
+        <v>723230</v>
       </c>
       <c r="R54" t="n">
-        <v>7216146</v>
+        <v>7216412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020107</v>
+        <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>91593</v>
+        <v>82861</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>65</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723230</v>
+        <v>723580</v>
       </c>
       <c r="R55" t="n">
-        <v>7216412</v>
+        <v>7216146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6090,32 +6090,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020097</v>
+        <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6125,10 +6125,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723576</v>
+        <v>723323</v>
       </c>
       <c r="R56" t="n">
-        <v>7216143</v>
+        <v>7216249</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020084</v>
+        <v>127020020</v>
       </c>
       <c r="B63" t="n">
-        <v>98450</v>
+        <v>90367</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723260</v>
+        <v>723341</v>
       </c>
       <c r="R63" t="n">
-        <v>7216304</v>
+        <v>7216126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,11 +6868,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6899,10 +6894,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020020</v>
+        <v>127020055</v>
       </c>
       <c r="B64" t="n">
-        <v>90367</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6910,34 +6905,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723341</v>
+        <v>723650</v>
       </c>
       <c r="R64" t="n">
-        <v>7216126</v>
+        <v>7216234</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6970,6 +6973,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6996,53 +7004,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>98450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723260</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7216304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1654,53 +1654,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127020059</v>
+        <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>91696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>723530</v>
+        <v>723592</v>
       </c>
       <c r="R12" t="n">
-        <v>7216208</v>
+        <v>7216220</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1733,11 +1725,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1764,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020095</v>
+        <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1775,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1799,10 +1786,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723589</v>
+        <v>723341</v>
       </c>
       <c r="R13" t="n">
-        <v>7216289</v>
+        <v>7215856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,32 +1848,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020023</v>
+        <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>91690</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1896,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723592</v>
+        <v>723589</v>
       </c>
       <c r="R14" t="n">
-        <v>7216220</v>
+        <v>7216289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1958,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020068</v>
+        <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>92815</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1969,34 +1956,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723341</v>
+        <v>723530</v>
       </c>
       <c r="R15" t="n">
-        <v>7215856</v>
+        <v>7216208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,6 +2024,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2055,32 +2055,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020109</v>
+        <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2090,10 +2090,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723233</v>
+        <v>723581</v>
       </c>
       <c r="R16" t="n">
-        <v>7216428</v>
+        <v>7216130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,32 +2152,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>92628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R17" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,32 +2346,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020079</v>
+        <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>92632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723330</v>
+        <v>723192</v>
       </c>
       <c r="R19" t="n">
-        <v>7216112</v>
+        <v>7216368</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,32 +2443,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>92626</v>
+        <v>78778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R20" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020067</v>
+        <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>92815</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,21 +2763,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723414</v>
+        <v>723104</v>
       </c>
       <c r="R23" t="n">
-        <v>7216002</v>
+        <v>7215946</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2849,7 +2849,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020093</v>
+        <v>127020101</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723104</v>
+        <v>723341</v>
       </c>
       <c r="R24" t="n">
-        <v>7215946</v>
+        <v>7215856</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>79638</v>
+        <v>92821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,21 +2957,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R25" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3043,10 +3043,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020101</v>
+        <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,21 +3054,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723341</v>
+        <v>723237</v>
       </c>
       <c r="R26" t="n">
-        <v>7215856</v>
+        <v>7216401</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020080</v>
+        <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>78778</v>
+        <v>98477</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723686</v>
+        <v>723541</v>
       </c>
       <c r="R30" t="n">
-        <v>7216284</v>
+        <v>7216191</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020081</v>
+        <v>127020080</v>
       </c>
       <c r="B31" t="n">
         <v>78778</v>
@@ -3594,10 +3594,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723396</v>
+        <v>723686</v>
       </c>
       <c r="R31" t="n">
-        <v>7215995</v>
+        <v>7216284</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020117</v>
+        <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78426</v>
+        <v>78778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723317</v>
+        <v>723396</v>
       </c>
       <c r="R32" t="n">
-        <v>7216136</v>
+        <v>7215995</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3753,32 +3753,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020057</v>
+        <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>98471</v>
+        <v>78426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723541</v>
+        <v>723317</v>
       </c>
       <c r="R33" t="n">
-        <v>7216191</v>
+        <v>7216136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3853,7 +3853,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92626</v>
+        <v>92632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020017</v>
+        <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,34 +3958,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723183</v>
+        <v>723333</v>
       </c>
       <c r="R35" t="n">
-        <v>7216366</v>
+        <v>7216135</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4026,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020026</v>
+        <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,42 +4068,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723085</v>
+        <v>723183</v>
       </c>
       <c r="R36" t="n">
-        <v>7216102</v>
+        <v>7216366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,11 +4128,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020060</v>
+        <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723333</v>
+        <v>723085</v>
       </c>
       <c r="R37" t="n">
-        <v>7216135</v>
+        <v>7216102</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,10 +4569,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4580,34 +4580,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R41" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4640,6 +4648,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4666,10 +4679,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020031</v>
+        <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,42 +4690,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723592</v>
+        <v>723486</v>
       </c>
       <c r="R42" t="n">
-        <v>7216060</v>
+        <v>7215989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4745,11 +4750,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4776,53 +4776,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020047</v>
+        <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723244</v>
+        <v>723372</v>
       </c>
       <c r="R43" t="n">
-        <v>7216446</v>
+        <v>7215992</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4855,11 +4847,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4886,45 +4873,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020100</v>
+        <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723372</v>
+        <v>723244</v>
       </c>
       <c r="R44" t="n">
-        <v>7215992</v>
+        <v>7216446</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4957,6 +4952,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4986,7 +4986,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020056</v>
+        <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>57823</v>
+        <v>91338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5188,42 +5188,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723286</v>
+        <v>723587</v>
       </c>
       <c r="R47" t="n">
-        <v>7216268</v>
+        <v>7216223</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5256,11 +5248,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5397,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020024</v>
+        <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>91332</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5408,34 +5395,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723587</v>
+        <v>723286</v>
       </c>
       <c r="R49" t="n">
-        <v>7216223</v>
+        <v>7216268</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5468,6 +5463,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5494,10 +5494,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020082</v>
+        <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>78778</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5505,34 +5505,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723348</v>
+        <v>723526</v>
       </c>
       <c r="R50" t="n">
-        <v>7215836</v>
+        <v>7216153</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5565,6 +5573,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5591,10 +5604,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020053</v>
+        <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>57823</v>
+        <v>78779</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5602,42 +5615,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723526</v>
+        <v>723330</v>
       </c>
       <c r="R51" t="n">
-        <v>7216153</v>
+        <v>7216136</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,17 +5677,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Lock</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5701,10 +5702,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020070</v>
+        <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5712,21 +5713,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5736,10 +5737,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723330</v>
+        <v>723348</v>
       </c>
       <c r="R52" t="n">
-        <v>7216136</v>
+        <v>7215836</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5780,7 +5781,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5799,32 +5799,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020097</v>
+        <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>91599</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723576</v>
+        <v>723230</v>
       </c>
       <c r="R53" t="n">
-        <v>7216143</v>
+        <v>7216412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5896,32 +5896,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020107</v>
+        <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>91593</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723230</v>
+        <v>723576</v>
       </c>
       <c r="R54" t="n">
-        <v>7216412</v>
+        <v>7216143</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6093,7 +6093,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6797,32 +6797,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020020</v>
+        <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>90367</v>
+        <v>98456</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723341</v>
+        <v>723260</v>
       </c>
       <c r="R63" t="n">
-        <v>7216126</v>
+        <v>7216304</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6868,6 +6868,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6894,10 +6899,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020055</v>
+        <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>90373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6905,42 +6910,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723650</v>
+        <v>723341</v>
       </c>
       <c r="R64" t="n">
-        <v>7216234</v>
+        <v>7216126</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6973,11 +6970,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7004,45 +6996,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>98450</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R65" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92634</v>
+        <v>92640</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7320,7 +7320,7 @@
         <v>127735569</v>
       </c>
       <c r="B68" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7421,6 +7421,2059 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128791708</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92224</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>723125</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7216351</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128791682</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>723157</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7216412</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128791575</v>
+      </c>
+      <c r="B71" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>723230</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7216421</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128791675</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>723223</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7216406</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Bilder</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128791681</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>723187</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7216406</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128791715</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>723186</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7216409</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128791569</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>723127</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7216349</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128791586</v>
+      </c>
+      <c r="B76" t="n">
+        <v>90499</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>723222</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7216415</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128791720</v>
+      </c>
+      <c r="B77" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>723235</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7216481</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128791571</v>
+      </c>
+      <c r="B78" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>723141</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7216343</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128791654</v>
+      </c>
+      <c r="B79" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>723195</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7216365</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128791673</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>723218</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7216431</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128791707</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92224</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>723212</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7216445</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128791674</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92760</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>723141</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7216343</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128791703</v>
+      </c>
+      <c r="B83" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>723221</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7216454</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128791714</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>723221</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7216454</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128791694</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>723143</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7216381</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128791680</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>723210</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7216448</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128791602</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90290</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>723147</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7216376</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128791627</v>
+      </c>
+      <c r="B88" t="n">
+        <v>90968</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>723211</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7216411</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128791573</v>
+      </c>
+      <c r="B89" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vaxspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius pinophilus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>723152</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7216349</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7426,7 +7426,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92224</v>
+        <v>92225</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7719,32 +7719,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>92760</v>
+        <v>78846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R72" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7790,11 +7790,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7824,7 +7819,7 @@
         <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,32 +7913,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791715</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>78846</v>
+        <v>92761</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7953,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723186</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7989,6 +7984,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8015,10 +8015,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>86906</v>
+        <v>90499</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R75" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>90499</v>
+        <v>86906</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8123,21 +8123,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8147,10 +8147,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R76" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8212,7 +8212,7 @@
         <v>128791720</v>
       </c>
       <c r="B77" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92224</v>
+        <v>92225</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8792,32 +8792,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>78846</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8889,32 +8889,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B84" t="n">
-        <v>78846</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8989,7 +8989,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7426,7 +7426,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92225</v>
+        <v>92252</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86906</v>
+        <v>86933</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,32 +7719,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>78846</v>
+        <v>92796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R72" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,32 +7816,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92769</v>
+        <v>92788</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -7887,6 +7887,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7913,32 +7918,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>92761</v>
+        <v>78873</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7948,10 +7953,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R74" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7984,11 +7989,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8018,7 +8018,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86906</v>
+        <v>86933</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8209,32 +8209,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>92757</v>
+        <v>86933</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R77" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8306,32 +8306,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>86906</v>
+        <v>92784</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R78" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8406,7 +8406,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92225</v>
+        <v>92252</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86906</v>
+        <v>86933</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -8015,10 +8015,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B75" t="n">
-        <v>90526</v>
+        <v>86933</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8050,10 +8050,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R75" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B76" t="n">
-        <v>86933</v>
+        <v>90526</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8123,21 +8123,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8147,10 +8147,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R76" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8598,10 +8598,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92252</v>
+        <v>92788</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8609,21 +8609,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8695,10 +8695,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92788</v>
+        <v>92252</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8706,21 +8706,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7426,7 +7426,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92252</v>
+        <v>92257</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86933</v>
+        <v>86937</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128791569</v>
       </c>
       <c r="B75" t="n">
-        <v>86933</v>
+        <v>86937</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>128791586</v>
       </c>
       <c r="B76" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>86933</v>
+        <v>86937</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92252</v>
+        <v>92257</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86933</v>
+        <v>86937</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7426,7 +7426,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92257</v>
+        <v>92262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7719,32 +7719,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791681</v>
+        <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>92801</v>
+        <v>78877</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7754,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723187</v>
+        <v>723186</v>
       </c>
       <c r="R72" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,32 +7816,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791675</v>
+        <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>92793</v>
+        <v>92806</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723223</v>
+        <v>723187</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -7887,11 +7887,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7918,32 +7913,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791715</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>78877</v>
+        <v>92798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7953,10 +7948,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723186</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7989,6 +7984,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8018,7 +8018,7 @@
         <v>128791569</v>
       </c>
       <c r="B75" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>128791586</v>
       </c>
       <c r="B76" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8209,32 +8209,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B77" t="n">
-        <v>86937</v>
+        <v>92794</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R77" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8306,32 +8306,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B78" t="n">
-        <v>92789</v>
+        <v>86938</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8341,10 +8341,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R78" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8406,7 +8406,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8598,10 +8598,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92793</v>
+        <v>92262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8609,21 +8609,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8633,10 +8633,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R81" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8695,10 +8695,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92257</v>
+        <v>92798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8706,21 +8706,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R82" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8989,7 +8989,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91696</v>
+        <v>91862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,14 +1747,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>92989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,14 +1848,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,14 +1949,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,14 +2063,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,14 +2164,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92628</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,14 +2265,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,14 +2366,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92632</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,14 +2467,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,14 +2568,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,14 +2674,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2748,14 +2788,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2845,14 +2889,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,14 +2990,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>92821</v>
+        <v>92989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,14 +3091,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,14 +3192,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,14 +3310,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3348,14 +3412,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>56855</v>
+        <v>56907</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,14 +3526,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98477</v>
+        <v>98653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3555,14 +3627,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78778</v>
+        <v>78877</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3652,14 +3728,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78778</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3749,14 +3829,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78426</v>
+        <v>78523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3846,14 +3930,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92632</v>
+        <v>92798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,14 +4031,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57660</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4053,14 +4145,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,14 +4246,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,14 +4360,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4370,14 +4474,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,14 +4576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4565,14 +4677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,14 +4791,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79638</v>
+        <v>79739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,14 +4892,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4869,14 +4993,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56855</v>
+        <v>56907</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,14 +5107,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92628</v>
+        <v>92794</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,14 +5208,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92628</v>
+        <v>92794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5173,14 +5309,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91338</v>
+        <v>91504</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5270,14 +5410,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5380,14 +5524,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57823</v>
+        <v>57876</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5490,14 +5638,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57823</v>
+        <v>57876</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5600,14 +5752,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5698,14 +5854,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78778</v>
+        <v>78877</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5795,14 +5955,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91599</v>
+        <v>91765</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5892,14 +6056,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5989,14 +6157,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82861</v>
+        <v>82979</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6086,14 +6258,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92628</v>
+        <v>92794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6183,14 +6359,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,14 +6461,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,14 +6562,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6488,14 +6676,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57660</v>
+        <v>57713</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6598,14 +6790,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57767</v>
+        <v>57820</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6695,14 +6891,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78779</v>
+        <v>78878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6793,14 +6993,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98456</v>
+        <v>98632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6895,14 +7099,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90373</v>
+        <v>90536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6992,14 +7200,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>57876</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7102,14 +7314,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7199,14 +7415,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57663</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7313,7 +7533,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7719,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>92806</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7754,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R72" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7816,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92806</v>
+        <v>92798</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7851,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -7887,6 +8111,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7913,32 +8142,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>92798</v>
+        <v>78877</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7948,10 +8177,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R74" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7984,11 +8213,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -8239,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>86938</v>
+        <v>90536</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R75" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>90536</v>
+        <v>86938</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R76" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B83" t="n">
-        <v>78877</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>78877</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91862</v>
+        <v>91866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78523</v>
+        <v>78527</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92262</v>
+        <v>92266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86938</v>
+        <v>86942</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86938</v>
+        <v>86942</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>92794</v>
+        <v>86942</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R77" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>86938</v>
+        <v>92798</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R78" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92262</v>
+        <v>92802</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92798</v>
+        <v>92266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>78881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B84" t="n">
-        <v>78877</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86938</v>
+        <v>86942</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92802</v>
+        <v>92266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R81" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92266</v>
+        <v>92802</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R82" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91866</v>
+        <v>91871</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78527</v>
+        <v>78432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92266</v>
+        <v>92271</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86942</v>
+        <v>86947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86942</v>
+        <v>86947</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>86942</v>
+        <v>86947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92266</v>
+        <v>92271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86942</v>
+        <v>86947</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B83" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>78791</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91879</v>
+        <v>91882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791681</v>
+        <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>92823</v>
+        <v>78791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723187</v>
+        <v>723186</v>
       </c>
       <c r="R72" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791675</v>
+        <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>92815</v>
+        <v>92828</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723223</v>
+        <v>723187</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,11 +8111,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8142,32 +8137,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791715</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>78791</v>
+        <v>92820</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,10 +8172,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723186</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8213,6 +8208,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>92811</v>
+        <v>86957</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R77" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>86954</v>
+        <v>92816</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R78" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92279</v>
+        <v>92820</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92815</v>
+        <v>92284</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90343</v>
+        <v>90346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91022</v>
+        <v>91025</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86954</v>
+        <v>86957</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91882</v>
+        <v>91885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91784</v>
+        <v>91787</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86957</v>
+        <v>86960</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>92831</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R72" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92828</v>
+        <v>92823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,6 +8111,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8137,32 +8142,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>92820</v>
+        <v>78792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,10 +8177,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R74" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8208,11 +8213,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86957</v>
+        <v>86960</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B77" t="n">
-        <v>86957</v>
+        <v>92819</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R77" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B78" t="n">
-        <v>92816</v>
+        <v>86960</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R78" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92820</v>
+        <v>92287</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R81" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92284</v>
+        <v>92823</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R82" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>78792</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B84" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90346</v>
+        <v>90349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91025</v>
+        <v>91028</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86957</v>
+        <v>86960</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B72" t="n">
-        <v>92831</v>
+        <v>92823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R72" t="n">
         <v>7216406</v>
@@ -8014,6 +8014,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8040,32 +8045,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B73" t="n">
-        <v>92823</v>
+        <v>78792</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,10 +8080,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R73" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8111,11 +8116,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8142,32 +8142,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B74" t="n">
-        <v>78792</v>
+        <v>92831</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,10 +8177,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R74" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8239,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B75" t="n">
-        <v>90558</v>
+        <v>86960</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R75" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B76" t="n">
-        <v>86960</v>
+        <v>90558</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R76" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>92819</v>
+        <v>86960</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R77" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>86960</v>
+        <v>92819</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R78" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>92823</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R72" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8014,11 +8014,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8045,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>78792</v>
+        <v>92831</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8080,10 +8075,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R73" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8142,32 +8137,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>92831</v>
+        <v>92823</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,7 +8172,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
         <v>7216406</v>
@@ -8213,6 +8208,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92831</v>
+        <v>92823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,6 +8111,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8137,32 +8142,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>128791681</v>
       </c>
       <c r="B74" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,7 +8177,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723187</v>
       </c>
       <c r="R74" t="n">
         <v>7216406</v>
@@ -8208,11 +8213,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8239,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>86960</v>
+        <v>90558</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R75" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>90558</v>
+        <v>86960</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R76" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91885</v>
+        <v>91892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791675</v>
+        <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>92823</v>
+        <v>92838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723223</v>
+        <v>723187</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,11 +8111,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8142,32 +8137,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>92831</v>
+        <v>92830</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,7 +8172,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
         <v>7216406</v>
@@ -8213,6 +8208,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92287</v>
+        <v>92830</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92823</v>
+        <v>92294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9019,7 +9019,7 @@
         <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90349</v>
+        <v>90353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86960</v>
+        <v>86964</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791715</v>
+        <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>78796</v>
+        <v>92838</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723186</v>
+        <v>723187</v>
       </c>
       <c r="R72" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92838</v>
+        <v>92830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723223</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,6 +8111,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8137,32 +8142,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>92830</v>
+        <v>78796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,10 +8177,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723186</v>
       </c>
       <c r="R74" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8208,11 +8213,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92830</v>
+        <v>92294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R81" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92294</v>
+        <v>92830</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R82" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B83" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91892</v>
+        <v>91899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86964</v>
+        <v>86971</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>86964</v>
+        <v>86971</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B77" t="n">
-        <v>86964</v>
+        <v>92833</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R77" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B78" t="n">
-        <v>92826</v>
+        <v>86971</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R78" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90353</v>
+        <v>90360</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91032</v>
+        <v>91039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86964</v>
+        <v>86971</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91899</v>
+        <v>91901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>127020059</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>127020033</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>127020029</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>127020049</v>
       </c>
       <c r="B29" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>127020060</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>127020026</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>127020032</v>
       </c>
       <c r="B38" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127020031</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>127020047</v>
       </c>
       <c r="B44" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127020027</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>127020056</v>
       </c>
       <c r="B49" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>127020053</v>
       </c>
       <c r="B50" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>127020035</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>127020058</v>
       </c>
       <c r="B60" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>127020076</v>
       </c>
       <c r="B61" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>127020055</v>
       </c>
       <c r="B65" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>127020030</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86971</v>
+        <v>86973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>128791681</v>
       </c>
       <c r="B72" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>128791675</v>
       </c>
       <c r="B73" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>128791715</v>
       </c>
       <c r="B74" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8239,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B75" t="n">
-        <v>90569</v>
+        <v>86973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R75" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B76" t="n">
-        <v>86971</v>
+        <v>90571</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R76" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8436,7 +8436,7 @@
         <v>128791720</v>
       </c>
       <c r="B77" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>128791571</v>
       </c>
       <c r="B78" t="n">
-        <v>86971</v>
+        <v>86973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B84" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90360</v>
+        <v>90362</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91039</v>
+        <v>91041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86971</v>
+        <v>86973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -8433,32 +8433,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791720</v>
+        <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>92835</v>
+        <v>86973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723235</v>
+        <v>723141</v>
       </c>
       <c r="R77" t="n">
-        <v>7216481</v>
+        <v>7216343</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8530,32 +8530,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791571</v>
+        <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>86973</v>
+        <v>92835</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3690</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723141</v>
+        <v>723235</v>
       </c>
       <c r="R78" t="n">
-        <v>7216343</v>
+        <v>7216481</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B81" t="n">
-        <v>92303</v>
+        <v>92839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B82" t="n">
-        <v>92839</v>
+        <v>92303</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9016,32 +9016,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791714</v>
+        <v>128791703</v>
       </c>
       <c r="B83" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9113,32 +9113,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791703</v>
+        <v>128791714</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91901</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91803</v>
+        <v>91812</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128791708</v>
       </c>
       <c r="B69" t="n">
-        <v>92303</v>
+        <v>92317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>128791682</v>
       </c>
       <c r="B70" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>128791575</v>
       </c>
       <c r="B71" t="n">
-        <v>86973</v>
+        <v>86974</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7943,32 +7943,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791681</v>
+        <v>128791715</v>
       </c>
       <c r="B72" t="n">
-        <v>92847</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7978,10 +7978,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723187</v>
+        <v>723186</v>
       </c>
       <c r="R72" t="n">
-        <v>7216406</v>
+        <v>7216409</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8040,32 +8040,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791675</v>
+        <v>128791681</v>
       </c>
       <c r="B73" t="n">
-        <v>92839</v>
+        <v>92833</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723223</v>
+        <v>723187</v>
       </c>
       <c r="R73" t="n">
         <v>7216406</v>
@@ -8111,11 +8111,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Bilder</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8142,32 +8137,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791715</v>
+        <v>128791675</v>
       </c>
       <c r="B74" t="n">
-        <v>78798</v>
+        <v>92825</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8177,10 +8172,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723186</v>
+        <v>723223</v>
       </c>
       <c r="R74" t="n">
-        <v>7216409</v>
+        <v>7216406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8213,6 +8208,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8239,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791569</v>
+        <v>128791586</v>
       </c>
       <c r="B75" t="n">
-        <v>86973</v>
+        <v>90572</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723127</v>
+        <v>723222</v>
       </c>
       <c r="R75" t="n">
-        <v>7216349</v>
+        <v>7216415</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791586</v>
+        <v>128791569</v>
       </c>
       <c r="B76" t="n">
-        <v>90571</v>
+        <v>86974</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1962</v>
+        <v>3690</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723222</v>
+        <v>723127</v>
       </c>
       <c r="R76" t="n">
-        <v>7216415</v>
+        <v>7216349</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8436,7 +8436,7 @@
         <v>128791571</v>
       </c>
       <c r="B77" t="n">
-        <v>86973</v>
+        <v>86974</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>128791720</v>
       </c>
       <c r="B78" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>128791654</v>
       </c>
       <c r="B79" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>128791673</v>
       </c>
       <c r="B80" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8822,10 +8822,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791674</v>
+        <v>128791707</v>
       </c>
       <c r="B81" t="n">
-        <v>92839</v>
+        <v>92317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8833,21 +8833,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4365</v>
+        <v>1958</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723141</v>
+        <v>723212</v>
       </c>
       <c r="R81" t="n">
-        <v>7216343</v>
+        <v>7216445</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791707</v>
+        <v>128791674</v>
       </c>
       <c r="B82" t="n">
-        <v>92303</v>
+        <v>92825</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8930,21 +8930,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1958</v>
+        <v>4365</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8954,10 +8954,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723212</v>
+        <v>723141</v>
       </c>
       <c r="R82" t="n">
-        <v>7216445</v>
+        <v>7216343</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9213,7 +9213,7 @@
         <v>128791694</v>
       </c>
       <c r="B85" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>128791680</v>
       </c>
       <c r="B86" t="n">
-        <v>92847</v>
+        <v>92833</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>128791602</v>
       </c>
       <c r="B87" t="n">
-        <v>90362</v>
+        <v>90363</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>128791627</v>
       </c>
       <c r="B88" t="n">
-        <v>91041</v>
+        <v>91042</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>128791573</v>
       </c>
       <c r="B89" t="n">
-        <v>86973</v>
+        <v>86974</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>91911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>92826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91812</v>
+        <v>91813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91911</v>
+        <v>91914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78444</v>
+        <v>78446</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91813</v>
+        <v>91816</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91914</v>
+        <v>91916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>127020095</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>127020098</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127020018</v>
       </c>
       <c r="B18" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>127020079</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>127020093</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>127020101</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127020016</v>
       </c>
       <c r="B26" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>127020072</v>
       </c>
       <c r="B28" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>127020080</v>
       </c>
       <c r="B31" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>127020081</v>
       </c>
       <c r="B32" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>127020117</v>
       </c>
       <c r="B33" t="n">
-        <v>78446</v>
+        <v>78447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92829</v>
+        <v>92831</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>127020017</v>
       </c>
       <c r="B36" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>127020071</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>127020096</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>127020019</v>
       </c>
       <c r="B42" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>127020100</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>127020070</v>
       </c>
       <c r="B51" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>127020082</v>
       </c>
       <c r="B52" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>127020097</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>127020105</v>
       </c>
       <c r="B55" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         <v>127020073</v>
       </c>
       <c r="B57" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>127020094</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>127020069</v>
       </c>
       <c r="B62" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>127020099</v>
       </c>
       <c r="B66" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91916</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127020068</v>
       </c>
       <c r="B13" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>127020109</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>127020062</v>
       </c>
       <c r="B19" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>127020083</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>127020067</v>
       </c>
       <c r="B25" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>127020057</v>
       </c>
       <c r="B30" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>127020061</v>
       </c>
       <c r="B34" t="n">
-        <v>92831</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>127020111</v>
       </c>
       <c r="B45" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>127020112</v>
       </c>
       <c r="B46" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>127020024</v>
       </c>
       <c r="B47" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>127020107</v>
       </c>
       <c r="B53" t="n">
-        <v>91818</v>
+        <v>91822</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>127020110</v>
       </c>
       <c r="B56" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>127020084</v>
       </c>
       <c r="B63" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>127020020</v>
       </c>
       <c r="B64" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9698,6 +9698,430 @@
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129688658</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92868</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>723218</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7216421</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129688657</v>
+      </c>
+      <c r="B91" t="n">
+        <v>92868</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>723194</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7216362</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129688656</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92360</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>723254</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7216408</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129688655</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90614</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>723237</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7216423</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9700,10 +9700,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129688658</v>
+        <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92868</v>
+        <v>92873</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723218</v>
+        <v>723194</v>
       </c>
       <c r="R90" t="n">
-        <v>7216421</v>
+        <v>7216362</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9806,10 +9806,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129688657</v>
+        <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92868</v>
+        <v>92873</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9845,10 +9845,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723194</v>
+        <v>723218</v>
       </c>
       <c r="R91" t="n">
-        <v>7216362</v>
+        <v>7216421</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92360</v>
+        <v>92365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90614</v>
+        <v>90619</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92873</v>
+        <v>92874</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92873</v>
+        <v>92874</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92365</v>
+        <v>92366</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90619</v>
+        <v>90620</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92874</v>
+        <v>92879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92874</v>
+        <v>92879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92366</v>
+        <v>92371</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90620</v>
+        <v>90625</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92879</v>
+        <v>92883</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92879</v>
+        <v>92883</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92371</v>
+        <v>92375</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90625</v>
+        <v>90629</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92883</v>
+        <v>92885</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92883</v>
+        <v>92885</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92375</v>
+        <v>92377</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90629</v>
+        <v>90631</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92885</v>
+        <v>92888</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92885</v>
+        <v>92888</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92377</v>
+        <v>92380</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90631</v>
+        <v>90634</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92888</v>
+        <v>92891</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92888</v>
+        <v>92891</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92380</v>
+        <v>92383</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90634</v>
+        <v>90637</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92891</v>
+        <v>92892</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92891</v>
+        <v>92892</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90637</v>
+        <v>90638</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -9703,7 +9703,7 @@
         <v>129688657</v>
       </c>
       <c r="B90" t="n">
-        <v>92892</v>
+        <v>92909</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>129688658</v>
       </c>
       <c r="B91" t="n">
-        <v>92892</v>
+        <v>92909</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>129688656</v>
       </c>
       <c r="B92" t="n">
-        <v>92384</v>
+        <v>92401</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>129688655</v>
       </c>
       <c r="B93" t="n">
-        <v>90638</v>
+        <v>90655</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126585102</v>
       </c>
       <c r="B3" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>126585285</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>126585094</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>126585491</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126585362</v>
       </c>
       <c r="B7" t="n">
-        <v>98463</v>
+        <v>98457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126585576</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126585723</v>
+        <v>126585609</v>
       </c>
       <c r="B9" t="n">
-        <v>105462</v>
+        <v>97314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723251</v>
+        <v>723248</v>
       </c>
       <c r="R9" t="n">
-        <v>7216315</v>
+        <v>7216291</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126585609</v>
+        <v>126585723</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>105456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723248</v>
+        <v>723251</v>
       </c>
       <c r="R10" t="n">
-        <v>7216291</v>
+        <v>7216315</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126585671</v>
       </c>
       <c r="B11" t="n">
-        <v>105462</v>
+        <v>105456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2071,32 +2071,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020098</v>
+        <v>127020109</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723581</v>
+        <v>723233</v>
       </c>
       <c r="R16" t="n">
-        <v>7216130</v>
+        <v>7216428</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,32 +2172,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>127020018</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723548</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7215979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020018</v>
+        <v>127020098</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,21 +2284,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723548</v>
+        <v>723581</v>
       </c>
       <c r="R18" t="n">
-        <v>7215979</v>
+        <v>7216130</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,32 +2374,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020062</v>
+        <v>127020079</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723192</v>
+        <v>723330</v>
       </c>
       <c r="R19" t="n">
-        <v>7216368</v>
+        <v>7216112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,32 +2475,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020079</v>
+        <v>127020083</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723330</v>
+        <v>723241</v>
       </c>
       <c r="R20" t="n">
-        <v>7216112</v>
+        <v>7216310</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,6 +2546,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,10 +2581,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020062</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2587,21 +2592,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4365</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723192</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,11 +2652,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,10 +2682,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020033</v>
+        <v>127020093</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2693,42 +2693,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723480</v>
+        <v>723104</v>
       </c>
       <c r="R22" t="n">
-        <v>7215979</v>
+        <v>7215946</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2753,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,10 +2783,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020093</v>
+        <v>127020016</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2794,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2818,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723104</v>
+        <v>723237</v>
       </c>
       <c r="R23" t="n">
-        <v>7215946</v>
+        <v>7216401</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,10 +2985,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020067</v>
+        <v>127020033</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,34 +2996,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723414</v>
+        <v>723480</v>
       </c>
       <c r="R25" t="n">
-        <v>7216002</v>
+        <v>7215979</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,6 +3064,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3099,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020016</v>
+        <v>127020067</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3110,21 +3110,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3134,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723237</v>
+        <v>723414</v>
       </c>
       <c r="R26" t="n">
-        <v>7216401</v>
+        <v>7216002</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3534,32 +3534,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020057</v>
+        <v>127020081</v>
       </c>
       <c r="B30" t="n">
-        <v>98737</v>
+        <v>78801</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723541</v>
+        <v>723396</v>
       </c>
       <c r="R30" t="n">
-        <v>7216191</v>
+        <v>7215995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020081</v>
+        <v>127020117</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>78447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,21 +3747,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723396</v>
+        <v>723317</v>
       </c>
       <c r="R32" t="n">
-        <v>7215995</v>
+        <v>7216136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,32 +3837,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020117</v>
+        <v>127020057</v>
       </c>
       <c r="B33" t="n">
-        <v>78447</v>
+        <v>98737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723317</v>
+        <v>723541</v>
       </c>
       <c r="R33" t="n">
-        <v>7216136</v>
+        <v>7216191</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4153,10 +4153,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020017</v>
+        <v>127020026</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,34 +4164,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723183</v>
+        <v>723085</v>
       </c>
       <c r="R36" t="n">
-        <v>7216366</v>
+        <v>7216102</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,6 +4232,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4254,7 +4267,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>127020032</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4287,7 +4300,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4297,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723539</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7215974</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4337,7 +4350,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4368,10 +4381,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>127020017</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,42 +4392,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723183</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216366</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,11 +4452,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4584,10 +4584,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>127020019</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4595,21 +4595,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723486</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7215989</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020031</v>
+        <v>127020096</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,42 +4696,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723592</v>
+        <v>723595</v>
       </c>
       <c r="R41" t="n">
-        <v>7216060</v>
+        <v>7216276</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,11 +4756,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4799,10 +4786,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020019</v>
+        <v>127020031</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4810,34 +4797,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723486</v>
+        <v>723592</v>
       </c>
       <c r="R42" t="n">
-        <v>7215989</v>
+        <v>7216060</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,6 +4865,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5760,10 +5760,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020070</v>
+        <v>127020082</v>
       </c>
       <c r="B51" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5771,21 +5771,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723330</v>
+        <v>723348</v>
       </c>
       <c r="R51" t="n">
-        <v>7216136</v>
+        <v>7215836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5839,7 +5839,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5862,10 +5861,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020082</v>
+        <v>127020070</v>
       </c>
       <c r="B52" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5873,21 +5872,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5897,10 +5896,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723348</v>
+        <v>723330</v>
       </c>
       <c r="R52" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5941,6 +5940,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020097</v>
+        <v>127020105</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6075,21 +6075,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723576</v>
+        <v>723580</v>
       </c>
       <c r="R54" t="n">
-        <v>7216143</v>
+        <v>7216146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6165,32 +6165,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020110</v>
       </c>
       <c r="B55" t="n">
-        <v>82878</v>
+        <v>92831</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723323</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7216249</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6266,32 +6266,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020110</v>
+        <v>127020097</v>
       </c>
       <c r="B56" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723323</v>
+        <v>723576</v>
       </c>
       <c r="R56" t="n">
-        <v>7216249</v>
+        <v>7216143</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6684,10 +6684,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020058</v>
+        <v>127020069</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>78802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,42 +6695,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723561</v>
+        <v>723237</v>
       </c>
       <c r="R60" t="n">
-        <v>7216205</v>
+        <v>7216401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6765,17 +6757,13 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6798,27 +6786,27 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020076</v>
+        <v>127020058</v>
       </c>
       <c r="B61" t="n">
-        <v>57831</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6827,16 +6815,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723707</v>
+        <v>723561</v>
       </c>
       <c r="R61" t="n">
-        <v>7216227</v>
+        <v>7216205</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6869,6 +6865,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6899,32 +6900,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020069</v>
+        <v>127020076</v>
       </c>
       <c r="B62" t="n">
-        <v>78802</v>
+        <v>57831</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>103031</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6934,10 +6935,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723237</v>
+        <v>723707</v>
       </c>
       <c r="R62" t="n">
-        <v>7216401</v>
+        <v>7216227</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6978,7 +6979,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7001,45 +7001,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020084</v>
+        <v>127020055</v>
       </c>
       <c r="B63" t="n">
-        <v>98716</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723260</v>
+        <v>723650</v>
       </c>
       <c r="R63" t="n">
-        <v>7216304</v>
+        <v>7216234</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7076,7 +7084,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>I blom</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7208,53 +7216,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>127020084</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723260</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7216304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10122,6 +10122,312 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134434151</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79123</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>723077</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7216224</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134434152</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79123</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>723074</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7216065</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134434154</v>
+      </c>
+      <c r="B96" t="n">
+        <v>80481</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Bjurträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>723304</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7215923</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33030-2025 artfynd.xlsx
+++ b/artfynd/A 33030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379819</v>
+        <v>127020107</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723306</v>
+        <v>723230</v>
       </c>
       <c r="R2" t="n">
-        <v>7215934</v>
+        <v>7216412</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering, Sitter på gamal sälg ned mot fuktigare parti. Ganska torr.</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,60 +760,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126585102</v>
+        <v>127020108</v>
       </c>
       <c r="B3" t="n">
-        <v>80153</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723312</v>
+        <v>723747</v>
       </c>
       <c r="R3" t="n">
-        <v>7215920</v>
+        <v>7216301</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,60 +861,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126585285</v>
+        <v>127020024</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723281</v>
+        <v>723587</v>
       </c>
       <c r="R4" t="n">
-        <v>7216191</v>
+        <v>7216223</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -943,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,22 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126585094</v>
+        <v>127020105</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723310</v>
+        <v>723580</v>
       </c>
       <c r="R5" t="n">
-        <v>7215915</v>
+        <v>7216146</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1040,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1060,22 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126585491</v>
+        <v>128791707</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>723276</v>
+        <v>723212</v>
       </c>
       <c r="R6" t="n">
-        <v>7216268</v>
+        <v>7216445</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1137,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1157,60 +1164,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126585362</v>
+        <v>128791708</v>
       </c>
       <c r="B7" t="n">
-        <v>98463</v>
+        <v>92692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>723309</v>
+        <v>723125</v>
       </c>
       <c r="R7" t="n">
-        <v>7216242</v>
+        <v>7216351</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1234,12 +1241,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1254,22 +1266,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126585576</v>
+        <v>129688656</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>92692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,37 +1289,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>723253</v>
+        <v>723254</v>
       </c>
       <c r="R8" t="n">
-        <v>7216261</v>
+        <v>7216408</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1331,12 +1347,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1351,60 +1372,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126585723</v>
+        <v>127020020</v>
       </c>
       <c r="B9" t="n">
-        <v>105462</v>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>723251</v>
+        <v>723341</v>
       </c>
       <c r="R9" t="n">
-        <v>7216315</v>
+        <v>7216126</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1428,12 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1448,60 +1469,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126585609</v>
+        <v>128791586</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>90932</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>723248</v>
+        <v>723222</v>
       </c>
       <c r="R10" t="n">
-        <v>7216291</v>
+        <v>7216415</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1525,12 +1550,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,60 +1570,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126585671</v>
+        <v>129688655</v>
       </c>
       <c r="B11" t="n">
-        <v>105462</v>
+        <v>90932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Snottermyran, Snottermyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>723241</v>
+        <v>723237</v>
       </c>
       <c r="R11" t="n">
-        <v>7216303</v>
+        <v>7216423</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1622,12 +1651,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1642,12 +1676,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1657,7 +1691,7 @@
         <v>127020023</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>92281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,10 +1789,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127020068</v>
+        <v>127020067</v>
       </c>
       <c r="B13" t="n">
-        <v>91602</v>
+        <v>91962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,10 +1824,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>723341</v>
+        <v>723414</v>
       </c>
       <c r="R13" t="n">
-        <v>7215856</v>
+        <v>7216002</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1856,10 +1890,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127020095</v>
+        <v>127020068</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1867,21 +1901,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1891,10 +1925,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>723589</v>
+        <v>723341</v>
       </c>
       <c r="R14" t="n">
-        <v>7216289</v>
+        <v>7215856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,10 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127020059</v>
+        <v>128791569</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>87325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,42 +2002,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>3690</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>723530</v>
+        <v>723127</v>
       </c>
       <c r="R15" t="n">
-        <v>7216208</v>
+        <v>7216349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2030,17 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2063,18 +2084,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127020098</v>
+        <v>128791571</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>87325</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2082,34 +2099,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>723581</v>
+        <v>723141</v>
       </c>
       <c r="R16" t="n">
-        <v>7216130</v>
+        <v>7216343</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,12 +2153,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2164,53 +2181,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127020109</v>
+        <v>128791573</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>87325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>723233</v>
+        <v>723152</v>
       </c>
       <c r="R17" t="n">
-        <v>7216428</v>
+        <v>7216349</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2237,12 +2250,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,18 +2278,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127020018</v>
+        <v>128791575</v>
       </c>
       <c r="B18" t="n">
-        <v>79663</v>
+        <v>87325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,34 +2293,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>723548</v>
+        <v>723230</v>
       </c>
       <c r="R18" t="n">
-        <v>7215979</v>
+        <v>7216421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,12 +2347,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2366,53 +2375,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127020062</v>
+        <v>128791694</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>723192</v>
+        <v>723143</v>
       </c>
       <c r="R19" t="n">
-        <v>7216368</v>
+        <v>7216381</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,12 +2444,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2467,18 +2472,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127020079</v>
+        <v>128791722</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2486,34 +2487,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>723330</v>
+        <v>723113</v>
       </c>
       <c r="R20" t="n">
-        <v>7216112</v>
+        <v>7216364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2540,12 +2541,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2568,40 +2569,36 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127020083</v>
+        <v>127020109</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2611,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>723241</v>
+        <v>723233</v>
       </c>
       <c r="R21" t="n">
-        <v>7216310</v>
+        <v>7216428</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2647,11 +2644,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2682,10 +2674,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127020033</v>
+        <v>127020110</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2693,42 +2685,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>723480</v>
+        <v>723323</v>
       </c>
       <c r="R22" t="n">
-        <v>7215979</v>
+        <v>7216249</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,11 +2745,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,10 +2775,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127020093</v>
+        <v>127020111</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2807,21 +2786,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2831,10 +2810,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>723104</v>
+        <v>723538</v>
       </c>
       <c r="R23" t="n">
-        <v>7215946</v>
+        <v>7216303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,10 +2876,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127020101</v>
+        <v>127020112</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2908,21 +2887,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2932,10 +2911,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>723341</v>
+        <v>723697</v>
       </c>
       <c r="R24" t="n">
-        <v>7215856</v>
+        <v>7216227</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2998,10 +2977,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127020067</v>
+        <v>128791720</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>93197</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3009,34 +2988,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>723414</v>
+        <v>723235</v>
       </c>
       <c r="R25" t="n">
-        <v>7216002</v>
+        <v>7216481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,12 +3042,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3091,40 +3070,36 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127020016</v>
+        <v>127020061</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>93201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3134,10 +3109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>723237</v>
+        <v>723229</v>
       </c>
       <c r="R26" t="n">
-        <v>7216401</v>
+        <v>7216414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,57 +3175,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127020029</v>
+        <v>127020062</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>93201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>723513</v>
+        <v>723192</v>
       </c>
       <c r="R27" t="n">
-        <v>7216122</v>
+        <v>7216368</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,11 +3246,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hona, födosökande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3318,45 +3276,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127020072</v>
+        <v>128791654</v>
       </c>
       <c r="B28" t="n">
-        <v>78802</v>
+        <v>93201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>723485</v>
+        <v>723195</v>
       </c>
       <c r="R28" t="n">
-        <v>7216003</v>
+        <v>7216365</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3383,12 +3341,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3412,61 +3370,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127020049</v>
+        <v>128791672</v>
       </c>
       <c r="B29" t="n">
-        <v>56917</v>
+        <v>93201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>4365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>723659</v>
+        <v>723304</v>
       </c>
       <c r="R29" t="n">
-        <v>7216289</v>
+        <v>7216493</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,17 +3439,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3526,53 +3467,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127020057</v>
+        <v>128791673</v>
       </c>
       <c r="B30" t="n">
-        <v>98737</v>
+        <v>93201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>723541</v>
+        <v>723218</v>
       </c>
       <c r="R30" t="n">
-        <v>7216191</v>
+        <v>7216431</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3599,12 +3536,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3627,53 +3564,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127020080</v>
+        <v>128791674</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>93201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>723686</v>
+        <v>723141</v>
       </c>
       <c r="R31" t="n">
-        <v>7216284</v>
+        <v>7216343</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,12 +3633,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,53 +3661,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127020081</v>
+        <v>128791675</v>
       </c>
       <c r="B32" t="n">
-        <v>78801</v>
+        <v>93201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>723396</v>
+        <v>723223</v>
       </c>
       <c r="R32" t="n">
-        <v>7215995</v>
+        <v>7216406</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,12 +3730,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,53 +3763,53 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127020117</v>
+        <v>129688657</v>
       </c>
       <c r="B33" t="n">
-        <v>78447</v>
+        <v>93201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>723317</v>
+        <v>723194</v>
       </c>
       <c r="R33" t="n">
-        <v>7216136</v>
+        <v>7216362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,12 +3836,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3922,26 +3861,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127020061</v>
+        <v>129688658</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>93201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3966,17 +3901,21 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>723229</v>
+        <v>723218</v>
       </c>
       <c r="R34" t="n">
-        <v>7216414</v>
+        <v>7216421</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,12 +3942,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4023,26 +3967,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127020060</v>
+        <v>127735569</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>93209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4050,42 +3990,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>723333</v>
+        <v>723602</v>
       </c>
       <c r="R35" t="n">
-        <v>7216135</v>
+        <v>7216242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4112,17 +4048,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4137,26 +4073,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127020017</v>
+        <v>128791680</v>
       </c>
       <c r="B36" t="n">
-        <v>79663</v>
+        <v>93209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,34 +4096,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>723183</v>
+        <v>723210</v>
       </c>
       <c r="R36" t="n">
-        <v>7216366</v>
+        <v>7216448</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4218,12 +4150,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,18 +4178,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127020026</v>
+        <v>128791681</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>93209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,42 +4193,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>723085</v>
+        <v>723187</v>
       </c>
       <c r="R37" t="n">
-        <v>7216102</v>
+        <v>7216406</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4327,17 +4247,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4360,18 +4275,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127020032</v>
+        <v>128791682</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,42 +4290,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>723539</v>
+        <v>723157</v>
       </c>
       <c r="R38" t="n">
-        <v>7215974</v>
+        <v>7216412</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4441,17 +4344,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska (och äldre) ringhack</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4474,18 +4372,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127020071</v>
+        <v>128791634</v>
       </c>
       <c r="B39" t="n">
-        <v>78802</v>
+        <v>93223</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4493,34 +4387,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>5448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>723634</v>
+        <v>723259</v>
       </c>
       <c r="R39" t="n">
-        <v>7216228</v>
+        <v>7216491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,12 +4441,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4561,7 +4455,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4576,18 +4469,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127020096</v>
+        <v>128791636</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>93223</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4595,34 +4484,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>723595</v>
+        <v>723113</v>
       </c>
       <c r="R40" t="n">
-        <v>7216276</v>
+        <v>7216364</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,12 +4538,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4677,61 +4566,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127020031</v>
+        <v>128791602</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>90710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>723592</v>
+        <v>723147</v>
       </c>
       <c r="R41" t="n">
-        <v>7216060</v>
+        <v>7216376</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4758,17 +4635,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bild 2</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4791,53 +4668,49 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127020019</v>
+        <v>128791604</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>90710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>723486</v>
+        <v>723109</v>
       </c>
       <c r="R42" t="n">
-        <v>7215989</v>
+        <v>7216354</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4864,12 +4737,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4892,22 +4765,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127020100</v>
+        <v>127020093</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4935,10 +4804,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>723372</v>
+        <v>723104</v>
       </c>
       <c r="R43" t="n">
-        <v>7215992</v>
+        <v>7215946</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5001,53 +4870,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127020047</v>
+        <v>127020094</v>
       </c>
       <c r="B44" t="n">
-        <v>56917</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>723244</v>
+        <v>723509</v>
       </c>
       <c r="R44" t="n">
-        <v>7216446</v>
+        <v>7216058</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5080,11 +4941,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5115,32 +4971,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127020111</v>
+        <v>127020095</v>
       </c>
       <c r="B45" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5150,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>723538</v>
+        <v>723589</v>
       </c>
       <c r="R45" t="n">
-        <v>7216303</v>
+        <v>7216289</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5216,32 +5072,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127020112</v>
+        <v>127020096</v>
       </c>
       <c r="B46" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5251,10 +5107,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>723697</v>
+        <v>723595</v>
       </c>
       <c r="R46" t="n">
-        <v>7216227</v>
+        <v>7216276</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,32 +5173,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127020024</v>
+        <v>127020097</v>
       </c>
       <c r="B47" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5352,10 +5208,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>723587</v>
+        <v>723576</v>
       </c>
       <c r="R47" t="n">
-        <v>7216223</v>
+        <v>7216143</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5418,53 +5274,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127020027</v>
+        <v>127020098</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>723273</v>
+        <v>723581</v>
       </c>
       <c r="R48" t="n">
-        <v>7216111</v>
+        <v>7216130</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5497,11 +5345,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5532,53 +5375,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127020056</v>
+        <v>127020099</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>723286</v>
+        <v>723570</v>
       </c>
       <c r="R49" t="n">
-        <v>7216268</v>
+        <v>7216008</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5611,11 +5446,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5646,53 +5476,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127020053</v>
+        <v>127020100</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>723526</v>
+        <v>723372</v>
       </c>
       <c r="R50" t="n">
-        <v>7216153</v>
+        <v>7215992</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5725,11 +5547,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5760,32 +5577,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127020070</v>
+        <v>127020101</v>
       </c>
       <c r="B51" t="n">
-        <v>78802</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5795,10 +5612,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>723330</v>
+        <v>723341</v>
       </c>
       <c r="R51" t="n">
-        <v>7216136</v>
+        <v>7215856</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5839,7 +5656,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5862,10 +5678,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127020082</v>
+        <v>127020117</v>
       </c>
       <c r="B52" t="n">
-        <v>78801</v>
+        <v>78730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5873,21 +5689,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5897,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>723348</v>
+        <v>723317</v>
       </c>
       <c r="R52" t="n">
-        <v>7215836</v>
+        <v>7216136</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5963,32 +5779,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127020107</v>
+        <v>127020079</v>
       </c>
       <c r="B53" t="n">
-        <v>91822</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5998,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>723230</v>
+        <v>723330</v>
       </c>
       <c r="R53" t="n">
-        <v>7216412</v>
+        <v>7216112</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6064,10 +5880,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127020097</v>
+        <v>127020080</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6075,21 +5891,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6099,10 +5915,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>723576</v>
+        <v>723686</v>
       </c>
       <c r="R54" t="n">
-        <v>7216143</v>
+        <v>7216284</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6165,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127020105</v>
+        <v>127020081</v>
       </c>
       <c r="B55" t="n">
-        <v>82878</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6176,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6200,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>723580</v>
+        <v>723396</v>
       </c>
       <c r="R55" t="n">
-        <v>7216146</v>
+        <v>7215995</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6266,32 +6082,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127020110</v>
+        <v>127020082</v>
       </c>
       <c r="B56" t="n">
-        <v>92831</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6301,10 +6117,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>723323</v>
+        <v>723348</v>
       </c>
       <c r="R56" t="n">
-        <v>7216249</v>
+        <v>7215836</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6367,10 +6183,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127020073</v>
+        <v>128791714</v>
       </c>
       <c r="B57" t="n">
-        <v>78802</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6378,34 +6194,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>723348</v>
+        <v>723221</v>
       </c>
       <c r="R57" t="n">
-        <v>7215836</v>
+        <v>7216454</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6432,12 +6248,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6446,7 +6262,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6461,18 +6276,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127020094</v>
+        <v>128791715</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6480,34 +6291,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Mönnforsen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>723509</v>
+        <v>723186</v>
       </c>
       <c r="R58" t="n">
-        <v>7216058</v>
+        <v>7216409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6534,12 +6345,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6562,18 +6373,14 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127020035</v>
+        <v>134434151</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79130</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6581,42 +6388,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>723333</v>
+        <v>723077</v>
       </c>
       <c r="R59" t="n">
-        <v>7215846</v>
+        <v>7216224</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6643,17 +6442,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6668,26 +6467,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127020058</v>
+        <v>134434152</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>79130</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6695,42 +6490,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>723561</v>
+        <v>723074</v>
       </c>
       <c r="R60" t="n">
-        <v>7216205</v>
+        <v>7216065</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6757,17 +6544,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre spår</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6782,48 +6569,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127020076</v>
+        <v>127020016</v>
       </c>
       <c r="B61" t="n">
-        <v>57831</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6833,10 +6616,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>723707</v>
+        <v>723237</v>
       </c>
       <c r="R61" t="n">
-        <v>7216227</v>
+        <v>7216401</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6899,10 +6682,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127020069</v>
+        <v>127020017</v>
       </c>
       <c r="B62" t="n">
-        <v>78802</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6910,21 +6693,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6934,10 +6717,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>723237</v>
+        <v>723183</v>
       </c>
       <c r="R62" t="n">
-        <v>7216401</v>
+        <v>7216366</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6978,7 +6761,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7001,32 +6783,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127020084</v>
+        <v>127020018</v>
       </c>
       <c r="B63" t="n">
-        <v>98716</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7036,10 +6818,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>723260</v>
+        <v>723548</v>
       </c>
       <c r="R63" t="n">
-        <v>7216304</v>
+        <v>7215979</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7072,11 +6854,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I blom</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7107,10 +6884,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127020020</v>
+        <v>127020019</v>
       </c>
       <c r="B64" t="n">
-        <v>90581</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7118,21 +6895,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7142,10 +6919,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>723341</v>
+        <v>723486</v>
       </c>
       <c r="R64" t="n">
-        <v>7216126</v>
+        <v>7215989</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7208,10 +6985,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127020055</v>
+        <v>126379819</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>80432</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7219,45 +6996,41 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>723650</v>
+        <v>723306</v>
       </c>
       <c r="R65" t="n">
-        <v>7216234</v>
+        <v>7215934</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7281,17 +7054,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering, Sitter på gamal sälg ned mot fuktigare parti. Ganska torr.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7306,26 +7079,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127020099</v>
+        <v>126585094</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7333,37 +7102,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>723570</v>
+        <v>723310</v>
       </c>
       <c r="R66" t="n">
-        <v>7216008</v>
+        <v>7215915</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7387,12 +7156,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7407,26 +7176,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127020030</v>
+        <v>134434154</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7434,46 +7199,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Slåttesmyran, Vb</t>
+          <t>Bjurträsk, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>723726</v>
+        <v>723304</v>
       </c>
       <c r="R67" t="n">
-        <v>7216246</v>
+        <v>7215923</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7500,17 +7253,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Hane, födosökande</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7525,26 +7278,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127735569</v>
+        <v>126585102</v>
       </c>
       <c r="B68" t="n">
-        <v>92754</v>
+        <v>80468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7552,41 +7301,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4366</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>723602</v>
+        <v>723312</v>
       </c>
       <c r="R68" t="n">
-        <v>7216242</v>
+        <v>7215920</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7610,17 +7355,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7635,57 +7375,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128791708</v>
+        <v>127020058</v>
       </c>
       <c r="B69" t="n">
-        <v>92317</v>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1958</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>723125</v>
+        <v>723561</v>
       </c>
       <c r="R69" t="n">
-        <v>7216351</v>
+        <v>7216205</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7712,17 +7460,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7745,14 +7493,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128791682</v>
+        <v>127020059</v>
       </c>
       <c r="B70" t="n">
-        <v>92833</v>
+        <v>57950</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7760,34 +7512,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>723157</v>
+        <v>723530</v>
       </c>
       <c r="R70" t="n">
-        <v>7216412</v>
+        <v>7216208</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7814,12 +7574,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7842,49 +7607,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128791575</v>
+        <v>127020060</v>
       </c>
       <c r="B71" t="n">
-        <v>86974</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3690</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>723230</v>
+        <v>723333</v>
       </c>
       <c r="R71" t="n">
-        <v>7216421</v>
+        <v>7216135</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7911,12 +7688,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7939,14 +7721,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128791715</v>
+        <v>127020026</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7954,34 +7740,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>723186</v>
+        <v>723085</v>
       </c>
       <c r="R72" t="n">
-        <v>7216409</v>
+        <v>7216102</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8008,12 +7802,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8036,49 +7835,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128791681</v>
+        <v>127020027</v>
       </c>
       <c r="B73" t="n">
-        <v>92833</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>723187</v>
+        <v>723273</v>
       </c>
       <c r="R73" t="n">
-        <v>7216406</v>
+        <v>7216111</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8105,12 +7916,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8133,49 +7949,65 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128791675</v>
+        <v>127020029</v>
       </c>
       <c r="B74" t="n">
-        <v>92825</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>723223</v>
+        <v>723513</v>
       </c>
       <c r="R74" t="n">
-        <v>7216406</v>
+        <v>7216122</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8202,17 +8034,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Bilder</t>
+          <t>Hona, födosökande</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8235,14 +8067,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128791586</v>
+        <v>127020030</v>
       </c>
       <c r="B75" t="n">
-        <v>90572</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,34 +8086,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>723222</v>
+        <v>723726</v>
       </c>
       <c r="R75" t="n">
-        <v>7216415</v>
+        <v>7216246</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8304,12 +8152,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Hane, födosökande</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8332,14 +8185,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128791569</v>
+        <v>127020031</v>
       </c>
       <c r="B76" t="n">
-        <v>86974</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8347,34 +8204,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>723127</v>
+        <v>723592</v>
       </c>
       <c r="R76" t="n">
-        <v>7216349</v>
+        <v>7216060</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8401,12 +8266,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8429,14 +8299,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128791571</v>
+        <v>127020032</v>
       </c>
       <c r="B77" t="n">
-        <v>86974</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8444,34 +8318,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3690</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>723141</v>
+        <v>723539</v>
       </c>
       <c r="R77" t="n">
-        <v>7216343</v>
+        <v>7215974</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8498,12 +8380,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska (och äldre) ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8526,49 +8413,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128791720</v>
+        <v>127020033</v>
       </c>
       <c r="B78" t="n">
-        <v>92821</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>723235</v>
+        <v>723480</v>
       </c>
       <c r="R78" t="n">
-        <v>7216481</v>
+        <v>7215979</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8595,12 +8494,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8623,49 +8527,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128791654</v>
+        <v>127020035</v>
       </c>
       <c r="B79" t="n">
-        <v>92825</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>723195</v>
+        <v>723333</v>
       </c>
       <c r="R79" t="n">
-        <v>7216365</v>
+        <v>7215846</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8692,12 +8608,17 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8706,7 +8627,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8721,49 +8641,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128791673</v>
+        <v>127020047</v>
       </c>
       <c r="B80" t="n">
-        <v>92825</v>
+        <v>57141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4365</v>
+        <v>100138</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>723218</v>
+        <v>723244</v>
       </c>
       <c r="R80" t="n">
-        <v>7216431</v>
+        <v>7216446</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8790,12 +8722,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8818,49 +8755,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128791707</v>
+        <v>127020049</v>
       </c>
       <c r="B81" t="n">
-        <v>92317</v>
+        <v>57141</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1958</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>723212</v>
+        <v>723659</v>
       </c>
       <c r="R81" t="n">
-        <v>7216445</v>
+        <v>7216289</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8887,12 +8836,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Uppstött</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8915,49 +8869,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128791674</v>
+        <v>127020053</v>
       </c>
       <c r="B82" t="n">
-        <v>92825</v>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>723141</v>
+        <v>723526</v>
       </c>
       <c r="R82" t="n">
-        <v>7216343</v>
+        <v>7216153</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8984,12 +8950,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9012,49 +8983,61 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128791703</v>
+        <v>127020055</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>58114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>723221</v>
+        <v>723650</v>
       </c>
       <c r="R83" t="n">
-        <v>7216454</v>
+        <v>7216234</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9081,12 +9064,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9109,14 +9097,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128791714</v>
+        <v>127020056</v>
       </c>
       <c r="B84" t="n">
-        <v>78798</v>
+        <v>58114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9124,34 +9116,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>723221</v>
+        <v>723286</v>
       </c>
       <c r="R84" t="n">
-        <v>7216454</v>
+        <v>7216268</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9178,12 +9178,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9206,14 +9211,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128791694</v>
+        <v>127020076</v>
       </c>
       <c r="B85" t="n">
-        <v>92813</v>
+        <v>58057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9221,34 +9230,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4361</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>723143</v>
+        <v>723707</v>
       </c>
       <c r="R85" t="n">
-        <v>7216381</v>
+        <v>7216227</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9275,12 +9284,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9303,14 +9312,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY85" t="inlineStr"/>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128791680</v>
+        <v>128791703</v>
       </c>
       <c r="B86" t="n">
-        <v>92833</v>
+        <v>8455</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9318,21 +9331,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9342,10 +9355,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>723210</v>
+        <v>723221</v>
       </c>
       <c r="R86" t="n">
-        <v>7216448</v>
+        <v>7216454</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9404,10 +9417,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128791602</v>
+        <v>126585285</v>
       </c>
       <c r="B87" t="n">
-        <v>90363</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9415,37 +9428,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>723147</v>
+        <v>723281</v>
       </c>
       <c r="R87" t="n">
-        <v>7216376</v>
+        <v>7216191</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9469,17 +9482,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Bild 2</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9494,57 +9502,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128791627</v>
+        <v>126585491</v>
       </c>
       <c r="B88" t="n">
-        <v>91042</v>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>723211</v>
+        <v>723276</v>
       </c>
       <c r="R88" t="n">
-        <v>7216411</v>
+        <v>7216268</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9571,12 +9579,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9591,60 +9599,60 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128791573</v>
+        <v>126585576</v>
       </c>
       <c r="B89" t="n">
-        <v>86974</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mönnforsen, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>723152</v>
+        <v>723253</v>
       </c>
       <c r="R89" t="n">
-        <v>7216349</v>
+        <v>7216261</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9668,12 +9676,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9688,22 +9696,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129688657</v>
+        <v>127020083</v>
       </c>
       <c r="B90" t="n">
-        <v>92909</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9711,38 +9719,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>723194</v>
+        <v>723241</v>
       </c>
       <c r="R90" t="n">
-        <v>7216362</v>
+        <v>7216310</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9769,17 +9773,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9794,22 +9798,26 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129688658</v>
+        <v>127020084</v>
       </c>
       <c r="B91" t="n">
-        <v>92909</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9817,38 +9825,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4365</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>723218</v>
+        <v>723260</v>
       </c>
       <c r="R91" t="n">
-        <v>7216421</v>
+        <v>7216304</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9875,17 +9879,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>I blom</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9900,64 +9904,64 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129688656</v>
+        <v>126585671</v>
       </c>
       <c r="B92" t="n">
-        <v>92401</v>
+        <v>106229</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1958</v>
+        <v>221725</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>723254</v>
+        <v>723241</v>
       </c>
       <c r="R92" t="n">
-        <v>7216408</v>
+        <v>7216303</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9981,17 +9985,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10006,64 +10005,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129688655</v>
+        <v>126585723</v>
       </c>
       <c r="B93" t="n">
-        <v>90655</v>
+        <v>106229</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1962</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>723237</v>
+        <v>723251</v>
       </c>
       <c r="R93" t="n">
-        <v>7216423</v>
+        <v>7216315</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10087,17 +10082,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10112,60 +10102,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134434151</v>
+        <v>126585609</v>
       </c>
       <c r="B94" t="n">
-        <v>79123</v>
+        <v>97983</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>723077</v>
+        <v>723248</v>
       </c>
       <c r="R94" t="n">
-        <v>7216224</v>
+        <v>7216291</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10189,17 +10179,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10214,60 +10199,60 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134434152</v>
+        <v>126585362</v>
       </c>
       <c r="B95" t="n">
-        <v>79123</v>
+        <v>99140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Snottermyran, Snottermyran, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>723074</v>
+        <v>723309</v>
       </c>
       <c r="R95" t="n">
-        <v>7216065</v>
+        <v>7216242</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10291,17 +10276,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10316,57 +10296,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134434154</v>
+        <v>127020057</v>
       </c>
       <c r="B96" t="n">
-        <v>80481</v>
+        <v>99140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Bjurträsk, Vb</t>
+          <t>Slåttesmyran, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>723304</v>
+        <v>723541</v>
       </c>
       <c r="R96" t="n">
-        <v>7215923</v>
+        <v>7216191</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10393,17 +10373,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10418,15 +10393,1106 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127020069</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>723237</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7216401</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127020070</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>723330</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7216136</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127020071</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>723634</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7216228</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127020072</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>723485</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7216003</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127020073</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Slåttesmyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>723348</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7215836</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128791627</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>723211</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7216411</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128791614</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>723235</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7216481</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128791686</v>
+      </c>
+      <c r="B104" t="n">
+        <v>93227</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6332402</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>nom. prov.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>723145</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7216375</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128791687</v>
+      </c>
+      <c r="B105" t="n">
+        <v>93227</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6332402</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>nom. prov.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>723187</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7216364</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128791688</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93227</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6332402</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>nom. prov.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>723239</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7216422</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128791689</v>
+      </c>
+      <c r="B107" t="n">
+        <v>93227</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6332402</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Phellodon resupinatus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>nom. prov.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Mönnforsen, Vb</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>723240</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7216414</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
